--- a/research/traditional_assets/database/data/tunisia/tunisia_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_drugs_pharmaceutical.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1903621821470889</v>
+        <v>0.1901148888738683</v>
       </c>
       <c r="C2">
-        <v>85.1035640339545</v>
+        <v>84.42711999588379</v>
       </c>
       <c r="D2">
-        <v>81.73356403395449</v>
+        <v>81.87361999588379</v>
       </c>
       <c r="E2">
-        <v>-9.949999999999999</v>
+        <v>-9.1335</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8165000000000001</v>
       </c>
       <c r="G2">
         <v>3.37</v>
@@ -1451,28 +1451,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04106995</v>
       </c>
       <c r="N2">
-        <v>8.22938775510204</v>
+        <v>8.18831780510204</v>
       </c>
       <c r="O2">
-        <v>1.234408163265306</v>
+        <v>1.228247670765306</v>
       </c>
       <c r="P2">
-        <v>6.994979591836734</v>
+        <v>6.960070134336734</v>
       </c>
       <c r="Q2">
-        <v>12.23497959183673</v>
+        <v>12.20007013433673</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1903621821470889</v>
+        <v>0.191603372599867</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8917152765285716</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>200.374915360307</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1901148888738683</v>
+        <v>0.1898675956006477</v>
       </c>
       <c r="C3">
-        <v>84.42711999588379</v>
+        <v>83.75115677235173</v>
       </c>
       <c r="D3">
-        <v>81.87361999588379</v>
+        <v>82.01415677235173</v>
       </c>
       <c r="E3">
-        <v>-9.1335</v>
+        <v>-8.316999999999998</v>
       </c>
       <c r="F3">
-        <v>0.8165000000000001</v>
+        <v>1.633</v>
       </c>
       <c r="G3">
         <v>3.37</v>
@@ -1533,28 +1533,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M3">
-        <v>0.04106995</v>
+        <v>0.0821399</v>
       </c>
       <c r="N3">
-        <v>8.18831780510204</v>
+        <v>8.147247855102041</v>
       </c>
       <c r="O3">
-        <v>1.228247670765306</v>
+        <v>1.222087178265306</v>
       </c>
       <c r="P3">
-        <v>6.960070134336734</v>
+        <v>6.925160676836735</v>
       </c>
       <c r="Q3">
-        <v>12.20007013433673</v>
+        <v>12.16516067683673</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.191603372599867</v>
+        <v>0.1928698934700487</v>
       </c>
       <c r="T3">
-        <v>0.8917152765285716</v>
+        <v>0.8994611605081052</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>200.374915360307</v>
+        <v>100.1874576801535</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1898675956006477</v>
+        <v>0.189620302327427</v>
       </c>
       <c r="C4">
-        <v>83.75115677235173</v>
+        <v>83.07567684358264</v>
       </c>
       <c r="D4">
-        <v>82.01415677235173</v>
+        <v>82.15517684358264</v>
       </c>
       <c r="E4">
-        <v>-8.316999999999998</v>
+        <v>-7.500499999999999</v>
       </c>
       <c r="F4">
-        <v>1.633</v>
+        <v>2.4495</v>
       </c>
       <c r="G4">
         <v>3.37</v>
@@ -1615,28 +1615,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M4">
-        <v>0.0821399</v>
+        <v>0.12320985</v>
       </c>
       <c r="N4">
-        <v>8.147247855102041</v>
+        <v>8.10617790510204</v>
       </c>
       <c r="O4">
-        <v>1.222087178265306</v>
+        <v>1.215926685765306</v>
       </c>
       <c r="P4">
-        <v>6.925160676836735</v>
+        <v>6.890251219336735</v>
       </c>
       <c r="Q4">
-        <v>12.16516067683673</v>
+        <v>12.13025121933673</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1928698934700487</v>
+        <v>0.1941625281726052</v>
       </c>
       <c r="T4">
-        <v>0.8994611605081052</v>
+        <v>0.9073667534356701</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.1874576801535</v>
+        <v>66.79163845343567</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.189620302327427</v>
+        <v>0.1893730090542064</v>
       </c>
       <c r="C5">
-        <v>83.07567684358264</v>
+        <v>82.40068270688873</v>
       </c>
       <c r="D5">
-        <v>82.15517684358264</v>
+        <v>82.29668270688873</v>
       </c>
       <c r="E5">
-        <v>-7.500499999999999</v>
+        <v>-6.683999999999999</v>
       </c>
       <c r="F5">
-        <v>2.4495</v>
+        <v>3.266</v>
       </c>
       <c r="G5">
         <v>3.37</v>
@@ -1697,28 +1697,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M5">
-        <v>0.12320985</v>
+        <v>0.1642798</v>
       </c>
       <c r="N5">
-        <v>8.10617790510204</v>
+        <v>8.065107955102041</v>
       </c>
       <c r="O5">
-        <v>1.215926685765306</v>
+        <v>1.209766193265306</v>
       </c>
       <c r="P5">
-        <v>6.890251219336735</v>
+        <v>6.855341761836735</v>
       </c>
       <c r="Q5">
-        <v>12.13025121933673</v>
+        <v>12.09534176183674</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1941625281726052</v>
+        <v>0.1954820927647983</v>
       </c>
       <c r="T5">
-        <v>0.9073667534356701</v>
+        <v>0.9154370462158928</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.79163845343567</v>
+        <v>50.09372884007676</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1893730090542064</v>
+        <v>0.1891257157809858</v>
       </c>
       <c r="C6">
-        <v>82.40068270688873</v>
+        <v>81.72617687681763</v>
       </c>
       <c r="D6">
-        <v>82.29668270688873</v>
+        <v>82.43867687681762</v>
       </c>
       <c r="E6">
-        <v>-6.683999999999999</v>
+        <v>-5.867499999999999</v>
       </c>
       <c r="F6">
-        <v>3.266</v>
+        <v>4.0825</v>
       </c>
       <c r="G6">
         <v>3.37</v>
@@ -1779,28 +1779,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M6">
-        <v>0.1642798</v>
+        <v>0.20534975</v>
       </c>
       <c r="N6">
-        <v>8.065107955102041</v>
+        <v>8.024038005102041</v>
       </c>
       <c r="O6">
-        <v>1.209766193265306</v>
+        <v>1.203605700765306</v>
       </c>
       <c r="P6">
-        <v>6.855341761836735</v>
+        <v>6.820432304336735</v>
       </c>
       <c r="Q6">
-        <v>12.09534176183674</v>
+        <v>12.06043230433674</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1954820927647983</v>
+        <v>0.1968294376641956</v>
       </c>
       <c r="T6">
-        <v>0.9154370462158928</v>
+        <v>0.9236772398967518</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.09372884007676</v>
+        <v>40.07498307206139</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1891257157809858</v>
+        <v>0.1888784225077651</v>
       </c>
       <c r="C7">
-        <v>81.72617687681763</v>
+        <v>81.05216188530129</v>
       </c>
       <c r="D7">
-        <v>82.43867687681762</v>
+        <v>82.58116188530128</v>
       </c>
       <c r="E7">
-        <v>-5.867499999999999</v>
+        <v>-5.050999999999998</v>
       </c>
       <c r="F7">
-        <v>4.0825</v>
+        <v>4.899000000000001</v>
       </c>
       <c r="G7">
         <v>3.37</v>
@@ -1861,28 +1861,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M7">
-        <v>0.20534975</v>
+        <v>0.2464197</v>
       </c>
       <c r="N7">
-        <v>8.024038005102041</v>
+        <v>7.982968055102041</v>
       </c>
       <c r="O7">
-        <v>1.203605700765306</v>
+        <v>1.197445208265306</v>
       </c>
       <c r="P7">
-        <v>6.820432304336735</v>
+        <v>6.785522846836734</v>
       </c>
       <c r="Q7">
-        <v>12.06043230433674</v>
+        <v>12.02552284683673</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1968294376641956</v>
+        <v>0.1982054494763459</v>
       </c>
       <c r="T7">
-        <v>0.9236772398967518</v>
+        <v>0.9320927568474162</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.07498307206139</v>
+        <v>33.39581922671783</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1888784225077651</v>
+        <v>0.1886311292345445</v>
       </c>
       <c r="C8">
-        <v>81.05216188530129</v>
+        <v>80.37864028180645</v>
       </c>
       <c r="D8">
-        <v>82.58116188530128</v>
+        <v>82.72414028180646</v>
       </c>
       <c r="E8">
-        <v>-5.050999999999999</v>
+        <v>-4.2345</v>
       </c>
       <c r="F8">
-        <v>4.899</v>
+        <v>5.7155</v>
       </c>
       <c r="G8">
         <v>3.37</v>
@@ -1943,28 +1943,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M8">
-        <v>0.2464197</v>
+        <v>0.28748965</v>
       </c>
       <c r="N8">
-        <v>7.982968055102041</v>
+        <v>7.94189810510204</v>
       </c>
       <c r="O8">
-        <v>1.197445208265306</v>
+        <v>1.191284715765306</v>
       </c>
       <c r="P8">
-        <v>6.785522846836734</v>
+        <v>6.750613389336734</v>
       </c>
       <c r="Q8">
-        <v>12.02552284683673</v>
+        <v>11.99061338933673</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1982054494763459</v>
+        <v>0.1996110529403704</v>
       </c>
       <c r="T8">
-        <v>0.9320927568474162</v>
+        <v>0.9406892526572347</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.39581922671783</v>
+        <v>28.62498790861529</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1886311292345445</v>
+        <v>0.1883838359613239</v>
       </c>
       <c r="C9">
-        <v>80.37864028180647</v>
+        <v>79.70561463348683</v>
       </c>
       <c r="D9">
-        <v>82.72414028180647</v>
+        <v>82.86761463348682</v>
       </c>
       <c r="E9">
-        <v>-4.234499999999998</v>
+        <v>-3.417999999999998</v>
       </c>
       <c r="F9">
-        <v>5.715500000000001</v>
+        <v>6.532000000000001</v>
       </c>
       <c r="G9">
         <v>3.37</v>
@@ -2025,28 +2025,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M9">
-        <v>0.28748965</v>
+        <v>0.3285596</v>
       </c>
       <c r="N9">
-        <v>7.94189810510204</v>
+        <v>7.90082815510204</v>
       </c>
       <c r="O9">
-        <v>1.191284715765306</v>
+        <v>1.185124223265306</v>
       </c>
       <c r="P9">
-        <v>6.750613389336734</v>
+        <v>6.715703931836734</v>
       </c>
       <c r="Q9">
-        <v>11.99061338933673</v>
+        <v>11.95570393183673</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1996110529403704</v>
+        <v>0.201047213001439</v>
       </c>
       <c r="T9">
-        <v>0.9406892526572347</v>
+        <v>0.949472628810745</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.62498790861528</v>
+        <v>25.04686442003837</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1883838359613239</v>
+        <v>0.1881365426881032</v>
       </c>
       <c r="C10">
-        <v>79.70561463348683</v>
+        <v>79.0330875253366</v>
       </c>
       <c r="D10">
-        <v>82.86761463348682</v>
+        <v>83.01158752533659</v>
       </c>
       <c r="E10">
-        <v>-3.417999999999998</v>
+        <v>-2.601499999999999</v>
       </c>
       <c r="F10">
-        <v>6.532000000000001</v>
+        <v>7.3485</v>
       </c>
       <c r="G10">
         <v>3.37</v>
@@ -2107,28 +2107,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M10">
-        <v>0.3285596</v>
+        <v>0.36962955</v>
       </c>
       <c r="N10">
-        <v>7.90082815510204</v>
+        <v>7.85975820510204</v>
       </c>
       <c r="O10">
-        <v>1.185124223265306</v>
+        <v>1.178963730765306</v>
       </c>
       <c r="P10">
-        <v>6.715703931836734</v>
+        <v>6.680794474336734</v>
       </c>
       <c r="Q10">
-        <v>11.95570393183673</v>
+        <v>11.92079447433673</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.201047213001439</v>
+        <v>0.2025149370198936</v>
       </c>
       <c r="T10">
-        <v>0.949472628810745</v>
+        <v>0.9584490461983982</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.04686442003837</v>
+        <v>22.26387948447855</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1881365426881032</v>
+        <v>0.1878892494148826</v>
       </c>
       <c r="C11">
-        <v>79.0330875253366</v>
+        <v>78.36106156034566</v>
       </c>
       <c r="D11">
-        <v>83.01158752533659</v>
+        <v>83.15606156034566</v>
       </c>
       <c r="E11">
-        <v>-2.601499999999999</v>
+        <v>-1.785</v>
       </c>
       <c r="F11">
-        <v>7.3485</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="G11">
         <v>3.37</v>
@@ -2189,28 +2189,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M11">
-        <v>0.36962955</v>
+        <v>0.4106994999999999</v>
       </c>
       <c r="N11">
-        <v>7.85975820510204</v>
+        <v>7.818688255102041</v>
       </c>
       <c r="O11">
-        <v>1.178963730765306</v>
+        <v>1.172803238265306</v>
       </c>
       <c r="P11">
-        <v>6.680794474336734</v>
+        <v>6.645885016836734</v>
       </c>
       <c r="Q11">
-        <v>11.92079447433673</v>
+        <v>11.88588501683673</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2025149370198936</v>
+        <v>0.2040152771276474</v>
       </c>
       <c r="T11">
-        <v>0.9584490461983982</v>
+        <v>0.9676249395279996</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.26387948447855</v>
+        <v>20.0374915360307</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1878892494148826</v>
+        <v>0.187641956141662</v>
       </c>
       <c r="C12">
-        <v>78.36106156034566</v>
+        <v>77.68953935965673</v>
       </c>
       <c r="D12">
-        <v>83.15606156034566</v>
+        <v>83.30103935965673</v>
       </c>
       <c r="E12">
-        <v>-1.784999999999998</v>
+        <v>-0.9684999999999988</v>
       </c>
       <c r="F12">
-        <v>8.165000000000001</v>
+        <v>8.9815</v>
       </c>
       <c r="G12">
         <v>3.37</v>
@@ -2271,28 +2271,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M12">
-        <v>0.4106995000000001</v>
+        <v>0.45176945</v>
       </c>
       <c r="N12">
-        <v>7.818688255102041</v>
+        <v>7.77761830510204</v>
       </c>
       <c r="O12">
-        <v>1.172803238265306</v>
+        <v>1.166642745765306</v>
       </c>
       <c r="P12">
-        <v>6.645885016836734</v>
+        <v>6.610975559336734</v>
       </c>
       <c r="Q12">
-        <v>11.88588501683673</v>
+        <v>11.85097555933674</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2040152771276474</v>
+        <v>0.2055493327434404</v>
       </c>
       <c r="T12">
-        <v>0.9676249395279996</v>
+        <v>0.9770070327077039</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.0374915360307</v>
+        <v>18.21590139639154</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.187641956141662</v>
+        <v>0.1873946628684414</v>
       </c>
       <c r="C13">
-        <v>77.68953935965673</v>
+        <v>77.01852356272353</v>
       </c>
       <c r="D13">
-        <v>83.30103935965673</v>
+        <v>83.44652356272353</v>
       </c>
       <c r="E13">
-        <v>-0.9684999999999988</v>
+        <v>-0.1519999999999992</v>
       </c>
       <c r="F13">
-        <v>8.9815</v>
+        <v>9.798</v>
       </c>
       <c r="G13">
         <v>3.37</v>
@@ -2353,28 +2353,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M13">
-        <v>0.45176945</v>
+        <v>0.4928394</v>
       </c>
       <c r="N13">
-        <v>7.77761830510204</v>
+        <v>7.73654835510204</v>
       </c>
       <c r="O13">
-        <v>1.166642745765306</v>
+        <v>1.160482253265306</v>
       </c>
       <c r="P13">
-        <v>6.610975559336734</v>
+        <v>6.576066101836734</v>
       </c>
       <c r="Q13">
-        <v>11.85097555933674</v>
+        <v>11.81606610183673</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2055493327434404</v>
+        <v>0.2071182532595924</v>
       </c>
       <c r="T13">
-        <v>0.9770070327077039</v>
+        <v>0.9866023552778564</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.21590139639154</v>
+        <v>16.69790961335892</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1873946628684414</v>
+        <v>0.1871473695952207</v>
       </c>
       <c r="C14">
-        <v>77.01852356272353</v>
+        <v>76.34801682747126</v>
       </c>
       <c r="D14">
-        <v>83.44652356272353</v>
+        <v>83.59251682747126</v>
       </c>
       <c r="E14">
-        <v>-0.1519999999999992</v>
+        <v>0.6645000000000021</v>
       </c>
       <c r="F14">
-        <v>9.798</v>
+        <v>10.6145</v>
       </c>
       <c r="G14">
         <v>3.37</v>
@@ -2435,28 +2435,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M14">
-        <v>0.4928394</v>
+        <v>0.5339093500000001</v>
       </c>
       <c r="N14">
-        <v>7.73654835510204</v>
+        <v>7.69547840510204</v>
       </c>
       <c r="O14">
-        <v>1.160482253265306</v>
+        <v>1.154321760765306</v>
       </c>
       <c r="P14">
-        <v>6.576066101836734</v>
+        <v>6.541156644336734</v>
       </c>
       <c r="Q14">
-        <v>11.81606610183673</v>
+        <v>11.78115664433673</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2071182532595924</v>
+        <v>0.2087232409140468</v>
       </c>
       <c r="T14">
-        <v>0.9866023552778564</v>
+        <v>0.9964182599760582</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.69790961335892</v>
+        <v>15.41345502771592</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1871473695952207</v>
+        <v>0.1869000763220001</v>
       </c>
       <c r="C15">
-        <v>76.34801682747126</v>
+        <v>75.67802183045825</v>
       </c>
       <c r="D15">
-        <v>83.59251682747126</v>
+        <v>83.73902183045824</v>
       </c>
       <c r="E15">
-        <v>0.6645000000000021</v>
+        <v>1.481000000000003</v>
       </c>
       <c r="F15">
-        <v>10.6145</v>
+        <v>11.431</v>
       </c>
       <c r="G15">
         <v>3.37</v>
@@ -2517,28 +2517,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M15">
-        <v>0.5339093500000001</v>
+        <v>0.5749793000000001</v>
       </c>
       <c r="N15">
-        <v>7.69547840510204</v>
+        <v>7.654408455102041</v>
       </c>
       <c r="O15">
-        <v>1.154321760765306</v>
+        <v>1.148161268265306</v>
       </c>
       <c r="P15">
-        <v>6.541156644336734</v>
+        <v>6.506247186836735</v>
       </c>
       <c r="Q15">
-        <v>11.78115664433673</v>
+        <v>11.74624718683673</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2087232409140468</v>
+        <v>0.2103655538627908</v>
       </c>
       <c r="T15">
-        <v>0.9964182599760582</v>
+        <v>1.006462441527707</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.41345502771592</v>
+        <v>14.31249395430764</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1869000763220001</v>
+        <v>0.1866527830487794</v>
       </c>
       <c r="C16">
-        <v>75.67802183045825</v>
+        <v>75.00854126703959</v>
       </c>
       <c r="D16">
-        <v>83.73902183045824</v>
+        <v>83.88604126703959</v>
       </c>
       <c r="E16">
-        <v>1.481000000000003</v>
+        <v>2.297500000000003</v>
       </c>
       <c r="F16">
-        <v>11.431</v>
+        <v>12.2475</v>
       </c>
       <c r="G16">
         <v>3.37</v>
@@ -2599,28 +2599,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M16">
-        <v>0.5749793000000001</v>
+        <v>0.6160492500000001</v>
       </c>
       <c r="N16">
-        <v>7.654408455102041</v>
+        <v>7.613338505102041</v>
       </c>
       <c r="O16">
-        <v>1.148161268265306</v>
+        <v>1.142000775765306</v>
       </c>
       <c r="P16">
-        <v>6.506247186836735</v>
+        <v>6.471337729336735</v>
       </c>
       <c r="Q16">
-        <v>11.74624718683673</v>
+        <v>11.71133772933674</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2103655538627908</v>
+        <v>0.2120465094691523</v>
       </c>
       <c r="T16">
-        <v>1.006462441527707</v>
+        <v>1.016742956762923</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.31249395430764</v>
+        <v>13.35832769068713</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1866527830487794</v>
+        <v>0.1866094897755588</v>
       </c>
       <c r="C17">
-        <v>75.00854126703959</v>
+        <v>74.21783286183735</v>
       </c>
       <c r="D17">
-        <v>83.88604126703959</v>
+        <v>83.91183286183735</v>
       </c>
       <c r="E17">
-        <v>2.297500000000001</v>
+        <v>3.114000000000003</v>
       </c>
       <c r="F17">
-        <v>12.2475</v>
+        <v>13.064</v>
       </c>
       <c r="G17">
         <v>3.37</v>
@@ -2681,45 +2681,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M17">
-        <v>0.61604925</v>
+        <v>0.6767152000000001</v>
       </c>
       <c r="N17">
-        <v>7.613338505102041</v>
+        <v>7.55267255510204</v>
       </c>
       <c r="O17">
-        <v>1.142000775765306</v>
+        <v>1.132900883265306</v>
       </c>
       <c r="P17">
-        <v>6.471337729336735</v>
+        <v>6.419771671836735</v>
       </c>
       <c r="Q17">
-        <v>11.71133772933674</v>
+        <v>11.65977167183673</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2120465094691523</v>
+        <v>0.2137674878280462</v>
       </c>
       <c r="T17">
-        <v>1.016742956762923</v>
+        <v>1.027268246170407</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.35832769068713</v>
+        <v>12.1607845591499</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1866094897755588</v>
+        <v>0.1863749465023382</v>
       </c>
       <c r="C18">
-        <v>74.21783286183735</v>
+        <v>73.54133615852034</v>
       </c>
       <c r="D18">
-        <v>83.91183286183735</v>
+        <v>84.05183615852033</v>
       </c>
       <c r="E18">
-        <v>3.114000000000003</v>
+        <v>3.930500000000002</v>
       </c>
       <c r="F18">
-        <v>13.064</v>
+        <v>13.8805</v>
       </c>
       <c r="G18">
         <v>3.37</v>
@@ -2763,28 +2763,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M18">
-        <v>0.6767152000000001</v>
+        <v>0.7190099000000001</v>
       </c>
       <c r="N18">
-        <v>7.55267255510204</v>
+        <v>7.510377855102041</v>
       </c>
       <c r="O18">
-        <v>1.132900883265306</v>
+        <v>1.126556678265306</v>
       </c>
       <c r="P18">
-        <v>6.419771671836735</v>
+        <v>6.383821176836735</v>
       </c>
       <c r="Q18">
-        <v>11.65977167183673</v>
+        <v>11.62382117683673</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2137674878280462</v>
+        <v>0.2155299355449858</v>
       </c>
       <c r="T18">
-        <v>1.027268246170407</v>
+        <v>1.038047157009396</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.1607845591499</v>
+        <v>11.44544429096462</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1863749465023382</v>
+        <v>0.1861404032291175</v>
       </c>
       <c r="C19">
-        <v>73.54133615852034</v>
+        <v>72.86530741497411</v>
       </c>
       <c r="D19">
-        <v>84.05183615852033</v>
+        <v>84.19230741497411</v>
       </c>
       <c r="E19">
-        <v>3.930500000000002</v>
+        <v>4.747000000000003</v>
       </c>
       <c r="F19">
-        <v>13.8805</v>
+        <v>14.697</v>
       </c>
       <c r="G19">
         <v>3.37</v>
@@ -2845,28 +2845,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M19">
-        <v>0.7190099000000001</v>
+        <v>0.7613046000000001</v>
       </c>
       <c r="N19">
-        <v>7.510377855102041</v>
+        <v>7.468083155102041</v>
       </c>
       <c r="O19">
-        <v>1.126556678265306</v>
+        <v>1.120212473265306</v>
       </c>
       <c r="P19">
-        <v>6.383821176836735</v>
+        <v>6.347870681836735</v>
       </c>
       <c r="Q19">
-        <v>11.62382117683673</v>
+        <v>11.58787068183674</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2155299355449858</v>
+        <v>0.2173353697916068</v>
       </c>
       <c r="T19">
-        <v>1.038047157009396</v>
+        <v>1.049088968112751</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.44544429096462</v>
+        <v>10.80958627479992</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1861404032291175</v>
+        <v>0.1859058599558969</v>
       </c>
       <c r="C20">
-        <v>72.8653074149741</v>
+        <v>72.1897489813534</v>
       </c>
       <c r="D20">
-        <v>84.1923074149741</v>
+        <v>84.33324898135341</v>
       </c>
       <c r="E20">
-        <v>4.747000000000002</v>
+        <v>5.563500000000001</v>
       </c>
       <c r="F20">
-        <v>14.697</v>
+        <v>15.5135</v>
       </c>
       <c r="G20">
         <v>3.37</v>
@@ -2927,28 +2927,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M20">
-        <v>0.7613046</v>
+        <v>0.8035993</v>
       </c>
       <c r="N20">
-        <v>7.468083155102041</v>
+        <v>7.42578845510204</v>
       </c>
       <c r="O20">
-        <v>1.120212473265306</v>
+        <v>1.113868268265306</v>
       </c>
       <c r="P20">
-        <v>6.347870681836735</v>
+        <v>6.311920186836734</v>
       </c>
       <c r="Q20">
-        <v>11.58787068183674</v>
+        <v>11.55192018683674</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2173353697916068</v>
+        <v>0.2191853826616011</v>
       </c>
       <c r="T20">
-        <v>1.049088968112751</v>
+        <v>1.0604034165273</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.80958627479992</v>
+        <v>10.24066068138939</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1859058599558969</v>
+        <v>0.1859603166826762</v>
       </c>
       <c r="C21">
-        <v>72.1897489813534</v>
+        <v>71.34048284035941</v>
       </c>
       <c r="D21">
-        <v>84.33324898135341</v>
+        <v>84.30048284035941</v>
       </c>
       <c r="E21">
-        <v>5.563500000000001</v>
+        <v>6.380000000000003</v>
       </c>
       <c r="F21">
-        <v>15.5135</v>
+        <v>16.33</v>
       </c>
       <c r="G21">
         <v>3.37</v>
@@ -3009,45 +3009,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M21">
-        <v>0.8035993</v>
+        <v>0.8736550000000001</v>
       </c>
       <c r="N21">
-        <v>7.42578845510204</v>
+        <v>7.35573275510204</v>
       </c>
       <c r="O21">
-        <v>1.113868268265306</v>
+        <v>1.103359913265306</v>
       </c>
       <c r="P21">
-        <v>6.311920186836734</v>
+        <v>6.252372841836734</v>
       </c>
       <c r="Q21">
-        <v>11.55192018683674</v>
+        <v>11.49237284183673</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2191853826616011</v>
+        <v>0.2210816458533453</v>
       </c>
       <c r="T21">
-        <v>1.0604034165273</v>
+        <v>1.072000726152212</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.24066068138939</v>
+        <v>9.419493684694805</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1859603166826762</v>
+        <v>0.1857402234094556</v>
       </c>
       <c r="C22">
-        <v>71.34048284035941</v>
+        <v>70.6565678023551</v>
       </c>
       <c r="D22">
-        <v>84.30048284035941</v>
+        <v>84.4330678023551</v>
       </c>
       <c r="E22">
-        <v>6.380000000000003</v>
+        <v>7.196500000000004</v>
       </c>
       <c r="F22">
-        <v>16.33</v>
+        <v>17.1465</v>
       </c>
       <c r="G22">
         <v>3.37</v>
@@ -3091,28 +3091,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M22">
-        <v>0.8736550000000001</v>
+        <v>0.9173377500000002</v>
       </c>
       <c r="N22">
-        <v>7.35573275510204</v>
+        <v>7.312050005102041</v>
       </c>
       <c r="O22">
-        <v>1.103359913265306</v>
+        <v>1.096807500765306</v>
       </c>
       <c r="P22">
-        <v>6.252372841836734</v>
+        <v>6.215242504336735</v>
       </c>
       <c r="Q22">
-        <v>11.49237284183673</v>
+        <v>11.45524250433673</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2210816458533453</v>
+        <v>0.2230259157081717</v>
       </c>
       <c r="T22">
-        <v>1.072000726152212</v>
+        <v>1.08389163855244</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.419493684694805</v>
+        <v>8.970946366376005</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1857402234094556</v>
+        <v>0.185520130136235</v>
       </c>
       <c r="C23">
-        <v>70.6565678023551</v>
+        <v>69.97307047163804</v>
       </c>
       <c r="D23">
-        <v>84.4330678023551</v>
+        <v>84.56607047163803</v>
       </c>
       <c r="E23">
-        <v>7.1965</v>
+        <v>8.013000000000002</v>
       </c>
       <c r="F23">
-        <v>17.1465</v>
+        <v>17.963</v>
       </c>
       <c r="G23">
         <v>3.37</v>
@@ -3173,28 +3173,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M23">
-        <v>0.91733775</v>
+        <v>0.9610205000000001</v>
       </c>
       <c r="N23">
-        <v>7.312050005102041</v>
+        <v>7.26836725510204</v>
       </c>
       <c r="O23">
-        <v>1.096807500765306</v>
+        <v>1.090255088265306</v>
       </c>
       <c r="P23">
-        <v>6.215242504336735</v>
+        <v>6.178112166836734</v>
       </c>
       <c r="Q23">
-        <v>11.45524250433673</v>
+        <v>11.41811216683674</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2230259157081717</v>
+        <v>0.2250200386361987</v>
       </c>
       <c r="T23">
-        <v>1.083891638552439</v>
+        <v>1.096087446142416</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.970946366376007</v>
+        <v>8.563176076995276</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.185520130136235</v>
+        <v>0.1853000368630144</v>
       </c>
       <c r="C24">
-        <v>69.97307047163804</v>
+        <v>69.2899928252951</v>
       </c>
       <c r="D24">
-        <v>84.56607047163803</v>
+        <v>84.6994928252951</v>
       </c>
       <c r="E24">
-        <v>8.013000000000002</v>
+        <v>8.829500000000003</v>
       </c>
       <c r="F24">
-        <v>17.963</v>
+        <v>18.7795</v>
       </c>
       <c r="G24">
         <v>3.37</v>
@@ -3255,28 +3255,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M24">
-        <v>0.9610205000000001</v>
+        <v>1.00470325</v>
       </c>
       <c r="N24">
-        <v>7.26836725510204</v>
+        <v>7.22468450510204</v>
       </c>
       <c r="O24">
-        <v>1.090255088265306</v>
+        <v>1.083702675765306</v>
       </c>
       <c r="P24">
-        <v>6.178112166836734</v>
+        <v>6.140981829336734</v>
       </c>
       <c r="Q24">
-        <v>11.41811216683674</v>
+        <v>11.38098182933673</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2250200386361987</v>
+        <v>0.2270659569649537</v>
       </c>
       <c r="T24">
-        <v>1.096087446142416</v>
+        <v>1.108600027955508</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.563176076995276</v>
+        <v>8.190864073647656</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1853000368630144</v>
+        <v>0.1850799435897937</v>
       </c>
       <c r="C25">
-        <v>69.2899928252951</v>
+        <v>68.60733685291009</v>
       </c>
       <c r="D25">
-        <v>84.6994928252951</v>
+        <v>84.83333685291009</v>
       </c>
       <c r="E25">
-        <v>8.829500000000003</v>
+        <v>9.646000000000004</v>
       </c>
       <c r="F25">
-        <v>18.7795</v>
+        <v>19.596</v>
       </c>
       <c r="G25">
         <v>3.37</v>
@@ -3337,28 +3337,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M25">
-        <v>1.00470325</v>
+        <v>1.048386</v>
       </c>
       <c r="N25">
-        <v>7.22468450510204</v>
+        <v>7.18100175510204</v>
       </c>
       <c r="O25">
-        <v>1.083702675765306</v>
+        <v>1.077150263265306</v>
       </c>
       <c r="P25">
-        <v>6.140981829336734</v>
+        <v>6.103851491836734</v>
       </c>
       <c r="Q25">
-        <v>11.38098182933673</v>
+        <v>11.34385149183673</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2270659569649537</v>
+        <v>0.2291657152497286</v>
       </c>
       <c r="T25">
-        <v>1.108600027955508</v>
+        <v>1.121441888237366</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.190864073647656</v>
+        <v>7.849578070579002</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1850799435897937</v>
+        <v>0.1850298503165731</v>
       </c>
       <c r="C26">
-        <v>68.60733685291009</v>
+        <v>67.82135889621853</v>
       </c>
       <c r="D26">
-        <v>84.83333685291009</v>
+        <v>84.86385889621853</v>
       </c>
       <c r="E26">
-        <v>9.646000000000001</v>
+        <v>10.4625</v>
       </c>
       <c r="F26">
-        <v>19.596</v>
+        <v>20.4125</v>
       </c>
       <c r="G26">
         <v>3.37</v>
@@ -3419,45 +3419,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M26">
-        <v>1.048386</v>
+        <v>1.10839875</v>
       </c>
       <c r="N26">
-        <v>7.181001755102041</v>
+        <v>7.12098900510204</v>
       </c>
       <c r="O26">
-        <v>1.077150263265306</v>
+        <v>1.068148350765306</v>
       </c>
       <c r="P26">
-        <v>6.103851491836735</v>
+        <v>6.052840654336734</v>
       </c>
       <c r="Q26">
-        <v>11.34385149183673</v>
+        <v>11.29284065433673</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2291657152497286</v>
+        <v>0.2313214670887641</v>
       </c>
       <c r="T26">
-        <v>1.121441888237366</v>
+        <v>1.13462619812674</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.849578070579005</v>
+        <v>7.424573291066991</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1850298503165731</v>
+        <v>0.1848165570433525</v>
       </c>
       <c r="C27">
-        <v>67.82135889621853</v>
+        <v>67.13506561854778</v>
       </c>
       <c r="D27">
-        <v>84.86385889621853</v>
+        <v>84.99406561854778</v>
       </c>
       <c r="E27">
-        <v>10.4625</v>
+        <v>11.279</v>
       </c>
       <c r="F27">
-        <v>20.4125</v>
+        <v>21.229</v>
       </c>
       <c r="G27">
         <v>3.37</v>
@@ -3501,28 +3501,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M27">
-        <v>1.10839875</v>
+        <v>1.1527347</v>
       </c>
       <c r="N27">
-        <v>7.12098900510204</v>
+        <v>7.076653055102041</v>
       </c>
       <c r="O27">
-        <v>1.068148350765306</v>
+        <v>1.061497958265306</v>
       </c>
       <c r="P27">
-        <v>6.052840654336734</v>
+        <v>6.015155096836734</v>
       </c>
       <c r="Q27">
-        <v>11.29284065433673</v>
+        <v>11.25515509683673</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2313214670887641</v>
+        <v>0.2335354824910168</v>
       </c>
       <c r="T27">
-        <v>1.13462619812674</v>
+        <v>1.148166840715827</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.424573291066991</v>
+        <v>7.139012779872107</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1848165570433525</v>
+        <v>0.1846032637701318</v>
       </c>
       <c r="C28">
-        <v>67.13506561854778</v>
+        <v>66.44917250751928</v>
       </c>
       <c r="D28">
-        <v>84.99406561854778</v>
+        <v>85.12467250751928</v>
       </c>
       <c r="E28">
-        <v>11.279</v>
+        <v>12.0955</v>
       </c>
       <c r="F28">
-        <v>21.229</v>
+        <v>22.0455</v>
       </c>
       <c r="G28">
         <v>3.37</v>
@@ -3583,28 +3583,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M28">
-        <v>1.1527347</v>
+        <v>1.19707065</v>
       </c>
       <c r="N28">
-        <v>7.076653055102041</v>
+        <v>7.03231710510204</v>
       </c>
       <c r="O28">
-        <v>1.061497958265306</v>
+        <v>1.054847565765306</v>
       </c>
       <c r="P28">
-        <v>6.015155096836734</v>
+        <v>5.977469539336734</v>
       </c>
       <c r="Q28">
-        <v>11.25515509683673</v>
+        <v>11.21746953933673</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2335354824910168</v>
+        <v>0.2358101558494957</v>
       </c>
       <c r="T28">
-        <v>1.148166840715827</v>
+        <v>1.162078459814205</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.139012779872107</v>
+        <v>6.874604899136102</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1846032637701318</v>
+        <v>0.1843899704969112</v>
       </c>
       <c r="C29">
-        <v>66.44917250751928</v>
+        <v>65.76368141073111</v>
       </c>
       <c r="D29">
-        <v>85.12467250751928</v>
+        <v>85.25568141073111</v>
       </c>
       <c r="E29">
-        <v>12.0955</v>
+        <v>12.91200000000001</v>
       </c>
       <c r="F29">
-        <v>22.0455</v>
+        <v>22.86200000000001</v>
       </c>
       <c r="G29">
         <v>3.37</v>
@@ -3665,28 +3665,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M29">
-        <v>1.19707065</v>
+        <v>1.2414066</v>
       </c>
       <c r="N29">
-        <v>7.03231710510204</v>
+        <v>6.98798115510204</v>
       </c>
       <c r="O29">
-        <v>1.054847565765306</v>
+        <v>1.048197173265306</v>
       </c>
       <c r="P29">
-        <v>5.977469539336734</v>
+        <v>5.939783981836734</v>
       </c>
       <c r="Q29">
-        <v>11.21746953933673</v>
+        <v>11.17978398183674</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2358101558494957</v>
+        <v>0.2381480145790434</v>
       </c>
       <c r="T29">
-        <v>1.162078459814205</v>
+        <v>1.176376512776426</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.874604899136102</v>
+        <v>6.629083295595527</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1843899704969112</v>
+        <v>0.1841766772236906</v>
       </c>
       <c r="C30">
-        <v>65.76368141073111</v>
+        <v>65.07859418717288</v>
       </c>
       <c r="D30">
-        <v>85.25568141073111</v>
+        <v>85.38709418717288</v>
       </c>
       <c r="E30">
-        <v>12.91200000000001</v>
+        <v>13.7285</v>
       </c>
       <c r="F30">
-        <v>22.86200000000001</v>
+        <v>23.6785</v>
       </c>
       <c r="G30">
         <v>3.37</v>
@@ -3747,28 +3747,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M30">
-        <v>1.2414066</v>
+        <v>1.28574255</v>
       </c>
       <c r="N30">
-        <v>6.98798115510204</v>
+        <v>6.94364520510204</v>
       </c>
       <c r="O30">
-        <v>1.048197173265306</v>
+        <v>1.041546780765306</v>
       </c>
       <c r="P30">
-        <v>5.939783981836734</v>
+        <v>5.902098424336734</v>
       </c>
       <c r="Q30">
-        <v>11.17978398183674</v>
+        <v>11.14209842433673</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2381480145790434</v>
+        <v>0.2405517284840712</v>
       </c>
       <c r="T30">
-        <v>1.176376512776426</v>
+        <v>1.191077327793921</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.629083295595527</v>
+        <v>6.400494216437061</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1841766772236906</v>
+        <v>0.1839633839504699</v>
       </c>
       <c r="C31">
-        <v>65.07859418717288</v>
+        <v>64.39391270731358</v>
       </c>
       <c r="D31">
-        <v>85.38709418717288</v>
+        <v>85.51891270731358</v>
       </c>
       <c r="E31">
-        <v>13.7285</v>
+        <v>14.545</v>
       </c>
       <c r="F31">
-        <v>23.6785</v>
+        <v>24.495</v>
       </c>
       <c r="G31">
         <v>3.37</v>
@@ -3829,28 +3829,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M31">
-        <v>1.28574255</v>
+        <v>1.3300785</v>
       </c>
       <c r="N31">
-        <v>6.94364520510204</v>
+        <v>6.899309255102041</v>
       </c>
       <c r="O31">
-        <v>1.041546780765306</v>
+        <v>1.034896388265306</v>
       </c>
       <c r="P31">
-        <v>5.902098424336734</v>
+        <v>5.864412866836735</v>
       </c>
       <c r="Q31">
-        <v>11.14209842433673</v>
+        <v>11.10441286683674</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2405517284840712</v>
+        <v>0.2430241199292428</v>
       </c>
       <c r="T31">
-        <v>1.191077327793921</v>
+        <v>1.20619816609763</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.400494216437062</v>
+        <v>6.187144409222493</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1839633839504699</v>
+        <v>0.1840135906772493</v>
       </c>
       <c r="C32">
-        <v>64.39391270731358</v>
+        <v>63.54634756629726</v>
       </c>
       <c r="D32">
-        <v>85.51891270731358</v>
+        <v>85.48784756629726</v>
       </c>
       <c r="E32">
-        <v>14.545</v>
+        <v>15.3615</v>
       </c>
       <c r="F32">
-        <v>24.495</v>
+        <v>25.3115</v>
       </c>
       <c r="G32">
         <v>3.37</v>
@@ -3911,45 +3911,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M32">
-        <v>1.3300785</v>
+        <v>1.39972595</v>
       </c>
       <c r="N32">
-        <v>6.899309255102041</v>
+        <v>6.82966180510204</v>
       </c>
       <c r="O32">
-        <v>1.034896388265306</v>
+        <v>1.024449270765306</v>
       </c>
       <c r="P32">
-        <v>5.864412866836735</v>
+        <v>5.805212534336734</v>
       </c>
       <c r="Q32">
-        <v>11.10441286683674</v>
+        <v>11.04521253433673</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2430241199292428</v>
+        <v>0.2455681748945642</v>
       </c>
       <c r="T32">
-        <v>1.20619816609763</v>
+        <v>1.221757289569562</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.187144409222493</v>
+        <v>5.879284980822167</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1840135906772493</v>
+        <v>0.1838087974040286</v>
       </c>
       <c r="C33">
-        <v>63.54634756629726</v>
+        <v>62.8567042337924</v>
       </c>
       <c r="D33">
-        <v>85.48784756629726</v>
+        <v>85.61470423379239</v>
       </c>
       <c r="E33">
-        <v>15.3615</v>
+        <v>16.178</v>
       </c>
       <c r="F33">
-        <v>25.3115</v>
+        <v>26.128</v>
       </c>
       <c r="G33">
         <v>3.37</v>
@@ -3993,28 +3993,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M33">
-        <v>1.39972595</v>
+        <v>1.4448784</v>
       </c>
       <c r="N33">
-        <v>6.82966180510204</v>
+        <v>6.78450935510204</v>
       </c>
       <c r="O33">
-        <v>1.024449270765306</v>
+        <v>1.017676403265306</v>
       </c>
       <c r="P33">
-        <v>5.805212534336734</v>
+        <v>5.766832951836734</v>
       </c>
       <c r="Q33">
-        <v>11.04521253433673</v>
+        <v>11.00683295183673</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2455681748945642</v>
+        <v>0.2481870550059245</v>
       </c>
       <c r="T33">
-        <v>1.221757289569562</v>
+        <v>1.23777403432008</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.879284980822167</v>
+        <v>5.695557325171474</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1838087974040286</v>
+        <v>0.183604004130808</v>
       </c>
       <c r="C34">
-        <v>62.8567042337924</v>
+        <v>62.16743794972426</v>
       </c>
       <c r="D34">
-        <v>85.61470423379239</v>
+        <v>85.74193794972426</v>
       </c>
       <c r="E34">
-        <v>16.178</v>
+        <v>16.9945</v>
       </c>
       <c r="F34">
-        <v>26.128</v>
+        <v>26.9445</v>
       </c>
       <c r="G34">
         <v>3.37</v>
@@ -4075,28 +4075,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M34">
-        <v>1.4448784</v>
+        <v>1.49003085</v>
       </c>
       <c r="N34">
-        <v>6.78450935510204</v>
+        <v>6.73935690510204</v>
       </c>
       <c r="O34">
-        <v>1.017676403265306</v>
+        <v>1.010903535765306</v>
       </c>
       <c r="P34">
-        <v>5.766832951836734</v>
+        <v>5.728453369336735</v>
       </c>
       <c r="Q34">
-        <v>11.00683295183673</v>
+        <v>10.96845336933674</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2481870550059245</v>
+        <v>0.2508841106429971</v>
       </c>
       <c r="T34">
-        <v>1.23777403432008</v>
+        <v>1.254268890854197</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.695557325171474</v>
+        <v>5.522964678954157</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.183604004130808</v>
+        <v>0.1833992108575874</v>
       </c>
       <c r="C35">
-        <v>62.16743794972426</v>
+        <v>61.47855039761236</v>
       </c>
       <c r="D35">
-        <v>85.74193794972426</v>
+        <v>85.86955039761236</v>
       </c>
       <c r="E35">
-        <v>16.9945</v>
+        <v>17.811</v>
       </c>
       <c r="F35">
-        <v>26.9445</v>
+        <v>27.761</v>
       </c>
       <c r="G35">
         <v>3.37</v>
@@ -4157,28 +4157,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M35">
-        <v>1.49003085</v>
+        <v>1.5351833</v>
       </c>
       <c r="N35">
-        <v>6.73935690510204</v>
+        <v>6.694204455102041</v>
       </c>
       <c r="O35">
-        <v>1.010903535765306</v>
+        <v>1.004130668265306</v>
       </c>
       <c r="P35">
-        <v>5.728453369336735</v>
+        <v>5.690073786836734</v>
       </c>
       <c r="Q35">
-        <v>10.96845336933674</v>
+        <v>10.93007378683673</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2508841106429971</v>
+        <v>0.2536628952387688</v>
       </c>
       <c r="T35">
-        <v>1.254268890854197</v>
+        <v>1.27126359152571</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.522964678954157</v>
+        <v>5.360524541337859</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1833992108575874</v>
+        <v>0.1831944175843668</v>
       </c>
       <c r="C36">
-        <v>61.47855039761236</v>
+        <v>60.79004327101356</v>
       </c>
       <c r="D36">
-        <v>85.86955039761236</v>
+        <v>85.99754327101355</v>
       </c>
       <c r="E36">
-        <v>17.811</v>
+        <v>18.6275</v>
       </c>
       <c r="F36">
-        <v>27.761</v>
+        <v>28.5775</v>
       </c>
       <c r="G36">
         <v>3.37</v>
@@ -4239,28 +4239,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M36">
-        <v>1.5351833</v>
+        <v>1.58033575</v>
       </c>
       <c r="N36">
-        <v>6.694204455102041</v>
+        <v>6.64905200510204</v>
       </c>
       <c r="O36">
-        <v>1.004130668265306</v>
+        <v>0.9973578007653059</v>
       </c>
       <c r="P36">
-        <v>5.690073786836734</v>
+        <v>5.651694204336734</v>
       </c>
       <c r="Q36">
-        <v>10.93007378683673</v>
+        <v>10.89169420433673</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2536628952387688</v>
+        <v>0.2565271808990258</v>
       </c>
       <c r="T36">
-        <v>1.27126359152571</v>
+        <v>1.28878120606404</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.360524541337859</v>
+        <v>5.207366697299633</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1831944175843668</v>
+        <v>0.1829896243111461</v>
       </c>
       <c r="C37">
-        <v>60.79004327101356</v>
+        <v>60.10191827359729</v>
       </c>
       <c r="D37">
-        <v>85.99754327101355</v>
+        <v>86.12591827359729</v>
       </c>
       <c r="E37">
-        <v>18.6275</v>
+        <v>19.44400000000001</v>
       </c>
       <c r="F37">
-        <v>28.5775</v>
+        <v>29.39400000000001</v>
       </c>
       <c r="G37">
         <v>3.37</v>
@@ -4321,28 +4321,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M37">
-        <v>1.58033575</v>
+        <v>1.6254882</v>
       </c>
       <c r="N37">
-        <v>6.64905200510204</v>
+        <v>6.60389955510204</v>
       </c>
       <c r="O37">
-        <v>0.9973578007653059</v>
+        <v>0.9905849332653059</v>
       </c>
       <c r="P37">
-        <v>5.651694204336734</v>
+        <v>5.613314621836734</v>
       </c>
       <c r="Q37">
-        <v>10.89169420433673</v>
+        <v>10.85331462183673</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2565271808990258</v>
+        <v>0.2594809754861658</v>
       </c>
       <c r="T37">
-        <v>1.28878120606404</v>
+        <v>1.306846246056692</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.207366697299633</v>
+        <v>5.062717622374644</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1829896243111461</v>
+        <v>0.1827848310379255</v>
       </c>
       <c r="C38">
-        <v>60.10191827359729</v>
+        <v>59.41417711922087</v>
       </c>
       <c r="D38">
-        <v>86.12591827359729</v>
+        <v>86.25467711922087</v>
       </c>
       <c r="E38">
-        <v>19.444</v>
+        <v>20.2605</v>
       </c>
       <c r="F38">
-        <v>29.394</v>
+        <v>30.2105</v>
       </c>
       <c r="G38">
         <v>3.37</v>
@@ -4403,28 +4403,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M38">
-        <v>1.6254882</v>
+        <v>1.67064065</v>
       </c>
       <c r="N38">
-        <v>6.60389955510204</v>
+        <v>6.55874710510204</v>
       </c>
       <c r="O38">
-        <v>0.9905849332653059</v>
+        <v>0.983812065765306</v>
       </c>
       <c r="P38">
-        <v>5.613314621836734</v>
+        <v>5.574935039336735</v>
       </c>
       <c r="Q38">
-        <v>10.85331462183673</v>
+        <v>10.81493503933673</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2594809754861658</v>
+        <v>0.2625285413300404</v>
       </c>
       <c r="T38">
-        <v>1.306846246056692</v>
+        <v>1.325484779382444</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.062717622374644</v>
+        <v>4.925887416364518</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1827848310379255</v>
+        <v>0.1825800377647049</v>
       </c>
       <c r="C39">
-        <v>59.41417711922087</v>
+        <v>58.72682153200586</v>
       </c>
       <c r="D39">
-        <v>86.25467711922087</v>
+        <v>86.38382153200585</v>
       </c>
       <c r="E39">
-        <v>20.2605</v>
+        <v>21.077</v>
       </c>
       <c r="F39">
-        <v>30.2105</v>
+        <v>31.027</v>
       </c>
       <c r="G39">
         <v>3.37</v>
@@ -4485,28 +4485,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M39">
-        <v>1.67064065</v>
+        <v>1.7157931</v>
       </c>
       <c r="N39">
-        <v>6.55874710510204</v>
+        <v>6.51359465510204</v>
       </c>
       <c r="O39">
-        <v>0.983812065765306</v>
+        <v>0.9770391982653061</v>
       </c>
       <c r="P39">
-        <v>5.574935039336735</v>
+        <v>5.536555456836735</v>
       </c>
       <c r="Q39">
-        <v>10.81493503933673</v>
+        <v>10.77655545683674</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2625285413300404</v>
+        <v>0.265674415749524</v>
       </c>
       <c r="T39">
-        <v>1.325484779382444</v>
+        <v>1.344724555718705</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.925887416364518</v>
+        <v>4.7962588001444</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1825800377647049</v>
+        <v>0.1823752444914842</v>
       </c>
       <c r="C40">
-        <v>58.72682153200586</v>
+        <v>58.03985324641512</v>
       </c>
       <c r="D40">
-        <v>86.38382153200585</v>
+        <v>86.51335324641512</v>
       </c>
       <c r="E40">
-        <v>21.077</v>
+        <v>21.8935</v>
       </c>
       <c r="F40">
-        <v>31.027</v>
+        <v>31.8435</v>
       </c>
       <c r="G40">
         <v>3.37</v>
@@ -4567,28 +4567,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M40">
-        <v>1.7157931</v>
+        <v>1.76094555</v>
       </c>
       <c r="N40">
-        <v>6.51359465510204</v>
+        <v>6.46844220510204</v>
       </c>
       <c r="O40">
-        <v>0.9770391982653061</v>
+        <v>0.9702663307653059</v>
       </c>
       <c r="P40">
-        <v>5.536555456836735</v>
+        <v>5.498175874336734</v>
       </c>
       <c r="Q40">
-        <v>10.77655545683674</v>
+        <v>10.73817587433673</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.265674415749524</v>
+        <v>0.2689234335925971</v>
       </c>
       <c r="T40">
-        <v>1.344724555718705</v>
+        <v>1.364595144393859</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.7962588001444</v>
+        <v>4.673277805268902</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1823752444914842</v>
+        <v>0.1821704512182636</v>
       </c>
       <c r="C41">
-        <v>58.03985324641512</v>
+        <v>57.35327400733035</v>
       </c>
       <c r="D41">
-        <v>86.51335324641512</v>
+        <v>86.64327400733035</v>
       </c>
       <c r="E41">
-        <v>21.8935</v>
+        <v>22.71</v>
       </c>
       <c r="F41">
-        <v>31.8435</v>
+        <v>32.66</v>
       </c>
       <c r="G41">
         <v>3.37</v>
@@ -4649,28 +4649,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M41">
-        <v>1.76094555</v>
+        <v>1.806098</v>
       </c>
       <c r="N41">
-        <v>6.46844220510204</v>
+        <v>6.42328975510204</v>
       </c>
       <c r="O41">
-        <v>0.9702663307653059</v>
+        <v>0.9634934632653059</v>
       </c>
       <c r="P41">
-        <v>5.498175874336734</v>
+        <v>5.459796291836734</v>
       </c>
       <c r="Q41">
-        <v>10.73817587433673</v>
+        <v>10.69979629183673</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2689234335925971</v>
+        <v>0.2722807520304393</v>
       </c>
       <c r="T41">
-        <v>1.364595144393859</v>
+        <v>1.385128086024852</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.673277805268902</v>
+        <v>4.556445860137179</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1821704512182636</v>
+        <v>0.182836907945043</v>
       </c>
       <c r="C42">
-        <v>57.35327400733035</v>
+        <v>56.11539852784617</v>
       </c>
       <c r="D42">
-        <v>86.64327400733035</v>
+        <v>86.22189852784616</v>
       </c>
       <c r="E42">
-        <v>22.71</v>
+        <v>23.5265</v>
       </c>
       <c r="F42">
-        <v>32.66</v>
+        <v>33.4765</v>
       </c>
       <c r="G42">
         <v>3.37</v>
@@ -4731,45 +4731,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M42">
-        <v>1.806098</v>
+        <v>1.9349417</v>
       </c>
       <c r="N42">
-        <v>6.42328975510204</v>
+        <v>6.29444605510204</v>
       </c>
       <c r="O42">
-        <v>0.9634934632653059</v>
+        <v>0.9441669082653059</v>
       </c>
       <c r="P42">
-        <v>5.459796291836734</v>
+        <v>5.350279146836734</v>
       </c>
       <c r="Q42">
-        <v>10.69979629183673</v>
+        <v>10.59027914683674</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2722807520304393</v>
+        <v>0.2757518778729542</v>
       </c>
       <c r="T42">
-        <v>1.385128086024852</v>
+        <v>1.406357059575539</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.556445860137179</v>
+        <v>4.253041709268057</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.182836907945043</v>
+        <v>0.1826533646718223</v>
       </c>
       <c r="C43">
-        <v>56.11539852784617</v>
+        <v>55.41453652854162</v>
       </c>
       <c r="D43">
-        <v>86.22189852784616</v>
+        <v>86.33753652854162</v>
       </c>
       <c r="E43">
-        <v>23.5265</v>
+        <v>24.34300000000001</v>
       </c>
       <c r="F43">
-        <v>33.4765</v>
+        <v>34.29300000000001</v>
       </c>
       <c r="G43">
         <v>3.37</v>
@@ -4813,28 +4813,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M43">
-        <v>1.9349417</v>
+        <v>1.9821354</v>
       </c>
       <c r="N43">
-        <v>6.29444605510204</v>
+        <v>6.24725235510204</v>
       </c>
       <c r="O43">
-        <v>0.9441669082653059</v>
+        <v>0.937087853265306</v>
       </c>
       <c r="P43">
-        <v>5.350279146836734</v>
+        <v>5.310164501836734</v>
       </c>
       <c r="Q43">
-        <v>10.59027914683674</v>
+        <v>10.55016450183673</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2757518778729542</v>
+        <v>0.2793426977100385</v>
       </c>
       <c r="T43">
-        <v>1.406357059575539</v>
+        <v>1.42831806669694</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.253041709268057</v>
+        <v>4.151778811428341</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1826533646718223</v>
+        <v>0.1824698213986017</v>
       </c>
       <c r="C44">
-        <v>55.41453652854162</v>
+        <v>54.71398512563562</v>
       </c>
       <c r="D44">
-        <v>86.33753652854162</v>
+        <v>86.45348512563562</v>
       </c>
       <c r="E44">
-        <v>24.343</v>
+        <v>25.1595</v>
       </c>
       <c r="F44">
-        <v>34.293</v>
+        <v>35.1095</v>
       </c>
       <c r="G44">
         <v>3.37</v>
@@ -4895,28 +4895,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M44">
-        <v>1.9821354</v>
+        <v>2.0293291</v>
       </c>
       <c r="N44">
-        <v>6.247252355102041</v>
+        <v>6.20005865510204</v>
       </c>
       <c r="O44">
-        <v>0.9370878532653061</v>
+        <v>0.930008798265306</v>
       </c>
       <c r="P44">
-        <v>5.310164501836734</v>
+        <v>5.270049856836734</v>
       </c>
       <c r="Q44">
-        <v>10.55016450183673</v>
+        <v>10.51004985683673</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2793426977100384</v>
+        <v>0.283059511225617</v>
       </c>
       <c r="T44">
-        <v>1.42831806669694</v>
+        <v>1.451049635471723</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.151778811428342</v>
+        <v>4.055225815813728</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1824698213986017</v>
+        <v>0.1835952781253811</v>
       </c>
       <c r="C45">
-        <v>54.71398512563562</v>
+        <v>53.19136763226524</v>
       </c>
       <c r="D45">
-        <v>86.45348512563562</v>
+        <v>85.74736763226524</v>
       </c>
       <c r="E45">
-        <v>25.1595</v>
+        <v>25.976</v>
       </c>
       <c r="F45">
-        <v>35.1095</v>
+        <v>35.926</v>
       </c>
       <c r="G45">
         <v>3.37</v>
@@ -4977,45 +4977,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M45">
-        <v>2.0293291</v>
+        <v>2.2022638</v>
       </c>
       <c r="N45">
-        <v>6.20005865510204</v>
+        <v>6.02712395510204</v>
       </c>
       <c r="O45">
-        <v>0.930008798265306</v>
+        <v>0.9040685932653059</v>
       </c>
       <c r="P45">
-        <v>5.270049856836734</v>
+        <v>5.123055361836734</v>
       </c>
       <c r="Q45">
-        <v>10.51004985683673</v>
+        <v>10.36305536183673</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.283059511225617</v>
+        <v>0.2869090680810376</v>
       </c>
       <c r="T45">
-        <v>1.451049635471723</v>
+        <v>1.474593045988463</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.055225815813728</v>
+        <v>3.736785645344594</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1835952781253811</v>
+        <v>0.1834414848521604</v>
       </c>
       <c r="C46">
-        <v>53.19136763226524</v>
+        <v>52.47067717945507</v>
       </c>
       <c r="D46">
-        <v>85.74736763226524</v>
+        <v>85.84317717945507</v>
       </c>
       <c r="E46">
-        <v>25.976</v>
+        <v>26.79250000000001</v>
       </c>
       <c r="F46">
-        <v>35.926</v>
+        <v>36.74250000000001</v>
       </c>
       <c r="G46">
         <v>3.37</v>
@@ -5059,28 +5059,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M46">
-        <v>2.2022638</v>
+        <v>2.252315250000001</v>
       </c>
       <c r="N46">
-        <v>6.02712395510204</v>
+        <v>5.97707250510204</v>
       </c>
       <c r="O46">
-        <v>0.9040685932653059</v>
+        <v>0.896560875765306</v>
       </c>
       <c r="P46">
-        <v>5.123055361836734</v>
+        <v>5.080511629336734</v>
       </c>
       <c r="Q46">
-        <v>10.36305536183673</v>
+        <v>10.32051162933674</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2869090680810376</v>
+        <v>0.2908986088221098</v>
       </c>
       <c r="T46">
-        <v>1.474593045988463</v>
+        <v>1.498992580523993</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.736785645344594</v>
+        <v>3.653745964336937</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1834414848521604</v>
+        <v>0.1832876915789398</v>
       </c>
       <c r="C47">
-        <v>52.47067717945507</v>
+        <v>51.7502010711247</v>
       </c>
       <c r="D47">
-        <v>85.84317717945507</v>
+        <v>85.9392010711247</v>
       </c>
       <c r="E47">
-        <v>26.79250000000001</v>
+        <v>27.60900000000001</v>
       </c>
       <c r="F47">
-        <v>36.74250000000001</v>
+        <v>37.559</v>
       </c>
       <c r="G47">
         <v>3.37</v>
@@ -5141,28 +5141,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M47">
-        <v>2.252315250000001</v>
+        <v>2.3023667</v>
       </c>
       <c r="N47">
-        <v>5.97707250510204</v>
+        <v>5.92702105510204</v>
       </c>
       <c r="O47">
-        <v>0.896560875765306</v>
+        <v>0.889053158265306</v>
       </c>
       <c r="P47">
-        <v>5.080511629336734</v>
+        <v>5.037967896836734</v>
       </c>
       <c r="Q47">
-        <v>10.32051162933674</v>
+        <v>10.27796789683673</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2908986088221098</v>
+        <v>0.29503591033137</v>
       </c>
       <c r="T47">
-        <v>1.498992580523993</v>
+        <v>1.524295801523803</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.653745964336937</v>
+        <v>3.574316704242656</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1832876915789398</v>
+        <v>0.1842524983057192</v>
       </c>
       <c r="C48">
-        <v>51.7502010711247</v>
+        <v>50.33483344286148</v>
       </c>
       <c r="D48">
-        <v>85.9392010711247</v>
+        <v>85.34033344286148</v>
       </c>
       <c r="E48">
-        <v>27.60900000000001</v>
+        <v>28.4255</v>
       </c>
       <c r="F48">
-        <v>37.559</v>
+        <v>38.3755</v>
       </c>
       <c r="G48">
         <v>3.37</v>
@@ -5223,45 +5223,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M48">
-        <v>2.3023667</v>
+        <v>2.459869550000001</v>
       </c>
       <c r="N48">
-        <v>5.92702105510204</v>
+        <v>5.76951820510204</v>
       </c>
       <c r="O48">
-        <v>0.889053158265306</v>
+        <v>0.865427730765306</v>
       </c>
       <c r="P48">
-        <v>5.037967896836734</v>
+        <v>4.904090474336734</v>
       </c>
       <c r="Q48">
-        <v>10.27796789683673</v>
+        <v>10.14409047433673</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.29503591033137</v>
+        <v>0.2993293364258852</v>
       </c>
       <c r="T48">
-        <v>1.524295801523803</v>
+        <v>1.550553861051907</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.574316704242656</v>
+        <v>3.345456979660583</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1842524983057192</v>
+        <v>0.1841225050324986</v>
       </c>
       <c r="C49">
-        <v>50.33483344286148</v>
+        <v>49.59853492041114</v>
       </c>
       <c r="D49">
-        <v>85.34033344286148</v>
+        <v>85.42053492041114</v>
       </c>
       <c r="E49">
-        <v>28.4255</v>
+        <v>29.24200000000001</v>
       </c>
       <c r="F49">
-        <v>38.3755</v>
+        <v>39.19200000000001</v>
       </c>
       <c r="G49">
         <v>3.37</v>
@@ -5305,28 +5305,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M49">
-        <v>2.459869550000001</v>
+        <v>2.512207200000001</v>
       </c>
       <c r="N49">
-        <v>5.76951820510204</v>
+        <v>5.71718055510204</v>
       </c>
       <c r="O49">
-        <v>0.865427730765306</v>
+        <v>0.8575770832653059</v>
       </c>
       <c r="P49">
-        <v>4.904090474336734</v>
+        <v>4.859603471836734</v>
       </c>
       <c r="Q49">
-        <v>10.14409047433673</v>
+        <v>10.09960347183673</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2993293364258852</v>
+        <v>0.3037878942932664</v>
       </c>
       <c r="T49">
-        <v>1.550553861051907</v>
+        <v>1.577821845946476</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.345456979660583</v>
+        <v>3.275759959250988</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1841225050324986</v>
+        <v>0.1839925117592779</v>
       </c>
       <c r="C50">
-        <v>49.59853492041115</v>
+        <v>48.86238728388729</v>
       </c>
       <c r="D50">
-        <v>85.42053492041114</v>
+        <v>85.50088728388729</v>
       </c>
       <c r="E50">
-        <v>29.242</v>
+        <v>30.05850000000001</v>
       </c>
       <c r="F50">
-        <v>39.192</v>
+        <v>40.00850000000001</v>
       </c>
       <c r="G50">
         <v>3.37</v>
@@ -5387,28 +5387,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M50">
-        <v>2.5122072</v>
+        <v>2.56454485</v>
       </c>
       <c r="N50">
-        <v>5.71718055510204</v>
+        <v>5.66484290510204</v>
       </c>
       <c r="O50">
-        <v>0.8575770832653059</v>
+        <v>0.8497264357653059</v>
       </c>
       <c r="P50">
-        <v>4.859603471836734</v>
+        <v>4.815116469336734</v>
       </c>
       <c r="Q50">
-        <v>10.09960347183673</v>
+        <v>10.05511646933673</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3037878942932664</v>
+        <v>0.3084212975672115</v>
       </c>
       <c r="T50">
-        <v>1.577821845946476</v>
+        <v>1.606159163582009</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.275759959250988</v>
+        <v>3.208907715184641</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1839925117592779</v>
+        <v>0.1838625184860573</v>
       </c>
       <c r="C51">
-        <v>48.86238728388729</v>
+        <v>48.12639095949147</v>
       </c>
       <c r="D51">
-        <v>85.50088728388729</v>
+        <v>85.58139095949147</v>
       </c>
       <c r="E51">
-        <v>30.05850000000001</v>
+        <v>30.875</v>
       </c>
       <c r="F51">
-        <v>40.00850000000001</v>
+        <v>40.825</v>
       </c>
       <c r="G51">
         <v>3.37</v>
@@ -5469,28 +5469,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M51">
-        <v>2.56454485</v>
+        <v>2.6168825</v>
       </c>
       <c r="N51">
-        <v>5.66484290510204</v>
+        <v>5.61250525510204</v>
       </c>
       <c r="O51">
-        <v>0.8497264357653059</v>
+        <v>0.841875788265306</v>
       </c>
       <c r="P51">
-        <v>4.815116469336734</v>
+        <v>4.770629466836733</v>
       </c>
       <c r="Q51">
-        <v>10.05511646933673</v>
+        <v>10.01062946683673</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3084212975672115</v>
+        <v>0.3132400369721146</v>
       </c>
       <c r="T51">
-        <v>1.606159163582009</v>
+        <v>1.635629973922964</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.208907715184641</v>
+        <v>3.144729560880949</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1838625184860573</v>
+        <v>0.1837325252128366</v>
       </c>
       <c r="C52">
-        <v>48.12639095949147</v>
+        <v>47.39054637503205</v>
       </c>
       <c r="D52">
-        <v>85.58139095949147</v>
+        <v>85.66204637503205</v>
       </c>
       <c r="E52">
-        <v>30.875</v>
+        <v>31.6915</v>
       </c>
       <c r="F52">
-        <v>40.825</v>
+        <v>41.6415</v>
       </c>
       <c r="G52">
         <v>3.37</v>
@@ -5551,28 +5551,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M52">
-        <v>2.6168825</v>
+        <v>2.66922015</v>
       </c>
       <c r="N52">
-        <v>5.61250525510204</v>
+        <v>5.56016760510204</v>
       </c>
       <c r="O52">
-        <v>0.841875788265306</v>
+        <v>0.834025140765306</v>
       </c>
       <c r="P52">
-        <v>4.770629466836733</v>
+        <v>4.726142464336735</v>
       </c>
       <c r="Q52">
-        <v>10.01062946683673</v>
+        <v>9.966142464336734</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3132400369721146</v>
+        <v>0.3182554596180339</v>
       </c>
       <c r="T52">
-        <v>1.635629973922964</v>
+        <v>1.666303674481916</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.144729560880949</v>
+        <v>3.083068196942107</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1837325252128366</v>
+        <v>0.183602531939616</v>
       </c>
       <c r="C53">
-        <v>47.39054637503205</v>
+        <v>46.65485395993147</v>
       </c>
       <c r="D53">
-        <v>85.66204637503205</v>
+        <v>85.74285395993147</v>
       </c>
       <c r="E53">
-        <v>31.6915</v>
+        <v>32.50800000000001</v>
       </c>
       <c r="F53">
-        <v>41.6415</v>
+        <v>42.45800000000001</v>
       </c>
       <c r="G53">
         <v>3.37</v>
@@ -5633,28 +5633,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M53">
-        <v>2.66922015</v>
+        <v>2.721557800000001</v>
       </c>
       <c r="N53">
-        <v>5.56016760510204</v>
+        <v>5.507829955102039</v>
       </c>
       <c r="O53">
-        <v>0.834025140765306</v>
+        <v>0.8261744932653059</v>
       </c>
       <c r="P53">
-        <v>4.726142464336735</v>
+        <v>4.681655461836733</v>
       </c>
       <c r="Q53">
-        <v>9.966142464336734</v>
+        <v>9.921655461836734</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3182554596180339</v>
+        <v>0.3234798582075333</v>
       </c>
       <c r="T53">
-        <v>1.666303674481916</v>
+        <v>1.698255445897491</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.083068196942107</v>
+        <v>3.023778423923988</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.183602531939616</v>
+        <v>0.1869864386663954</v>
       </c>
       <c r="C54">
-        <v>46.65485395993147</v>
+        <v>43.78329950123911</v>
       </c>
       <c r="D54">
-        <v>85.74285395993147</v>
+        <v>83.68779950123911</v>
       </c>
       <c r="E54">
-        <v>32.50800000000001</v>
+        <v>33.3245</v>
       </c>
       <c r="F54">
-        <v>42.45800000000001</v>
+        <v>43.2745</v>
       </c>
       <c r="G54">
         <v>3.37</v>
@@ -5715,45 +5715,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M54">
-        <v>2.721557800000001</v>
+        <v>3.111436550000001</v>
       </c>
       <c r="N54">
-        <v>5.507829955102039</v>
+        <v>5.11795120510204</v>
       </c>
       <c r="O54">
-        <v>0.8261744932653059</v>
+        <v>0.7676926807653059</v>
       </c>
       <c r="P54">
-        <v>4.681655461836733</v>
+        <v>4.350258524336734</v>
       </c>
       <c r="Q54">
-        <v>9.921655461836734</v>
+        <v>9.590258524336734</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3234798582075333</v>
+        <v>0.3289265716306284</v>
       </c>
       <c r="T54">
-        <v>1.698255445897491</v>
+        <v>1.731566867160538</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.023778423923988</v>
+        <v>2.64488368085219</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1869864386663954</v>
+        <v>0.1869227453931747</v>
       </c>
       <c r="C55">
-        <v>43.78329950123911</v>
+        <v>43.0045705201065</v>
       </c>
       <c r="D55">
-        <v>83.68779950123911</v>
+        <v>83.7255705201065</v>
       </c>
       <c r="E55">
-        <v>33.3245</v>
+        <v>34.14100000000001</v>
       </c>
       <c r="F55">
-        <v>43.2745</v>
+        <v>44.09100000000001</v>
       </c>
       <c r="G55">
         <v>3.37</v>
@@ -5797,28 +5797,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M55">
-        <v>3.111436550000001</v>
+        <v>3.170142900000001</v>
       </c>
       <c r="N55">
-        <v>5.11795120510204</v>
+        <v>5.059244855102039</v>
       </c>
       <c r="O55">
-        <v>0.7676926807653059</v>
+        <v>0.7588867282653059</v>
       </c>
       <c r="P55">
-        <v>4.350258524336734</v>
+        <v>4.300358126836733</v>
       </c>
       <c r="Q55">
-        <v>9.590258524336734</v>
+        <v>9.540358126836733</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3289265716306284</v>
+        <v>0.3346100986808146</v>
       </c>
       <c r="T55">
-        <v>1.731566867160538</v>
+        <v>1.766326611087196</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.64488368085219</v>
+        <v>2.595904353429001</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1869227453931747</v>
+        <v>0.1868590521199541</v>
       </c>
       <c r="C56">
-        <v>43.0045705201065</v>
+        <v>42.22587564894116</v>
       </c>
       <c r="D56">
-        <v>83.7255705201065</v>
+        <v>83.76337564894116</v>
       </c>
       <c r="E56">
-        <v>34.14100000000001</v>
+        <v>34.95750000000001</v>
       </c>
       <c r="F56">
-        <v>44.09100000000001</v>
+        <v>44.90750000000001</v>
       </c>
       <c r="G56">
         <v>3.37</v>
@@ -5879,28 +5879,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M56">
-        <v>3.170142900000001</v>
+        <v>3.228849250000001</v>
       </c>
       <c r="N56">
-        <v>5.059244855102039</v>
+        <v>5.00053850510204</v>
       </c>
       <c r="O56">
-        <v>0.7588867282653059</v>
+        <v>0.750080775765306</v>
       </c>
       <c r="P56">
-        <v>4.300358126836733</v>
+        <v>4.250457729336734</v>
       </c>
       <c r="Q56">
-        <v>9.540358126836733</v>
+        <v>9.490457729336734</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3346100986808146</v>
+        <v>0.3405462269332314</v>
       </c>
       <c r="T56">
-        <v>1.766326611087196</v>
+        <v>1.802631232521705</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.595904353429001</v>
+        <v>2.548706092457565</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1868590521199541</v>
+        <v>0.1867953588467335</v>
       </c>
       <c r="C57">
-        <v>42.22587564894116</v>
+        <v>41.44721493396961</v>
       </c>
       <c r="D57">
-        <v>83.76337564894116</v>
+        <v>83.80121493396962</v>
       </c>
       <c r="E57">
-        <v>34.95750000000001</v>
+        <v>35.77400000000002</v>
       </c>
       <c r="F57">
-        <v>44.90750000000001</v>
+        <v>45.72400000000001</v>
       </c>
       <c r="G57">
         <v>3.37</v>
@@ -5961,28 +5961,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M57">
-        <v>3.228849250000001</v>
+        <v>3.287555600000001</v>
       </c>
       <c r="N57">
-        <v>5.00053850510204</v>
+        <v>4.941832155102039</v>
       </c>
       <c r="O57">
-        <v>0.750080775765306</v>
+        <v>0.7412748232653059</v>
       </c>
       <c r="P57">
-        <v>4.250457729336734</v>
+        <v>4.200557331836734</v>
       </c>
       <c r="Q57">
-        <v>9.490457729336734</v>
+        <v>9.440557331836734</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3405462269332314</v>
+        <v>0.3467521791971215</v>
       </c>
       <c r="T57">
-        <v>1.802631232521705</v>
+        <v>1.840586064021418</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.548706092457565</v>
+        <v>2.503193483663679</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1867953588467335</v>
+        <v>0.1886212155735128</v>
       </c>
       <c r="C58">
-        <v>41.44721493396961</v>
+        <v>39.55938241950355</v>
       </c>
       <c r="D58">
-        <v>83.80121493396962</v>
+        <v>82.72988241950355</v>
       </c>
       <c r="E58">
-        <v>35.77400000000002</v>
+        <v>36.59050000000001</v>
       </c>
       <c r="F58">
-        <v>45.72400000000001</v>
+        <v>46.54050000000001</v>
       </c>
       <c r="G58">
         <v>3.37</v>
@@ -6043,45 +6043,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M58">
-        <v>3.287555600000001</v>
+        <v>3.527769900000001</v>
       </c>
       <c r="N58">
-        <v>4.941832155102039</v>
+        <v>4.70161785510204</v>
       </c>
       <c r="O58">
-        <v>0.7412748232653059</v>
+        <v>0.705242678265306</v>
       </c>
       <c r="P58">
-        <v>4.200557331836734</v>
+        <v>3.996375176836734</v>
       </c>
       <c r="Q58">
-        <v>9.440557331836734</v>
+        <v>9.236375176836734</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3467521791971215</v>
+        <v>0.3532467804035183</v>
       </c>
       <c r="T58">
-        <v>1.840586064021418</v>
+        <v>1.880306236521119</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.503193483663679</v>
+        <v>2.332745045276915</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1886212155735128</v>
+        <v>0.1885906723002922</v>
       </c>
       <c r="C59">
-        <v>39.55938241950355</v>
+        <v>38.76057854321768</v>
       </c>
       <c r="D59">
-        <v>82.72988241950355</v>
+        <v>82.74757854321768</v>
       </c>
       <c r="E59">
-        <v>36.59050000000001</v>
+        <v>37.40700000000001</v>
       </c>
       <c r="F59">
-        <v>46.54050000000001</v>
+        <v>47.35700000000001</v>
       </c>
       <c r="G59">
         <v>3.37</v>
@@ -6125,28 +6125,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M59">
-        <v>3.527769900000001</v>
+        <v>3.589660600000001</v>
       </c>
       <c r="N59">
-        <v>4.70161785510204</v>
+        <v>4.63972715510204</v>
       </c>
       <c r="O59">
-        <v>0.705242678265306</v>
+        <v>0.695959073265306</v>
       </c>
       <c r="P59">
-        <v>3.996375176836734</v>
+        <v>3.943768081836734</v>
       </c>
       <c r="Q59">
-        <v>9.236375176836734</v>
+        <v>9.183768081836735</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3532467804035183</v>
+        <v>0.3600506483340291</v>
       </c>
       <c r="T59">
-        <v>1.880306236521119</v>
+        <v>1.92191784580652</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.332745045276915</v>
+        <v>2.292525303116968</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1885906723002922</v>
+        <v>0.1885601290270715</v>
       </c>
       <c r="C60">
-        <v>38.76057854321769</v>
+        <v>37.96178223903962</v>
       </c>
       <c r="D60">
-        <v>82.74757854321768</v>
+        <v>82.76528223903962</v>
       </c>
       <c r="E60">
-        <v>37.407</v>
+        <v>38.2235</v>
       </c>
       <c r="F60">
-        <v>47.357</v>
+        <v>48.1735</v>
       </c>
       <c r="G60">
         <v>3.37</v>
@@ -6207,28 +6207,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M60">
-        <v>3.5896606</v>
+        <v>3.651551300000001</v>
       </c>
       <c r="N60">
-        <v>4.63972715510204</v>
+        <v>4.577836455102039</v>
       </c>
       <c r="O60">
-        <v>0.695959073265306</v>
+        <v>0.6866754682653059</v>
       </c>
       <c r="P60">
-        <v>3.943768081836734</v>
+        <v>3.891160986836733</v>
       </c>
       <c r="Q60">
-        <v>9.183768081836735</v>
+        <v>9.131160986836733</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.360050648334029</v>
+        <v>0.3671864122611501</v>
       </c>
       <c r="T60">
-        <v>1.921917845806519</v>
+        <v>1.965559289691208</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.292525303116969</v>
+        <v>2.253668942047189</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1885601290270715</v>
+        <v>0.1885295857538509</v>
       </c>
       <c r="C61">
-        <v>37.96178223903962</v>
+        <v>37.16299351183043</v>
       </c>
       <c r="D61">
-        <v>82.76528223903962</v>
+        <v>82.78299351183043</v>
       </c>
       <c r="E61">
-        <v>38.2235</v>
+        <v>39.04000000000001</v>
       </c>
       <c r="F61">
-        <v>48.1735</v>
+        <v>48.99</v>
       </c>
       <c r="G61">
         <v>3.37</v>
@@ -6289,28 +6289,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M61">
-        <v>3.651551300000001</v>
+        <v>3.713442000000001</v>
       </c>
       <c r="N61">
-        <v>4.577836455102039</v>
+        <v>4.51594575510204</v>
       </c>
       <c r="O61">
-        <v>0.6866754682653059</v>
+        <v>0.677391863265306</v>
       </c>
       <c r="P61">
-        <v>3.891160986836733</v>
+        <v>3.838553891836734</v>
       </c>
       <c r="Q61">
-        <v>9.131160986836733</v>
+        <v>9.078553891836734</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3671864122611501</v>
+        <v>0.3746789643846273</v>
       </c>
       <c r="T61">
-        <v>1.965559289691208</v>
+        <v>2.01138280577013</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.253668942047189</v>
+        <v>2.216107793013069</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1885295857538509</v>
+        <v>0.1884990424806303</v>
       </c>
       <c r="C62">
-        <v>37.16299351183043</v>
+        <v>36.36421236645555</v>
       </c>
       <c r="D62">
-        <v>82.78299351183043</v>
+        <v>82.80071236645554</v>
       </c>
       <c r="E62">
-        <v>39.04000000000001</v>
+        <v>39.8565</v>
       </c>
       <c r="F62">
-        <v>48.99</v>
+        <v>49.8065</v>
       </c>
       <c r="G62">
         <v>3.37</v>
@@ -6371,28 +6371,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M62">
-        <v>3.713442000000001</v>
+        <v>3.7753327</v>
       </c>
       <c r="N62">
-        <v>4.51594575510204</v>
+        <v>4.454055055102041</v>
       </c>
       <c r="O62">
-        <v>0.677391863265306</v>
+        <v>0.6681082582653061</v>
       </c>
       <c r="P62">
-        <v>3.838553891836734</v>
+        <v>3.785946796836734</v>
       </c>
       <c r="Q62">
-        <v>9.078553891836734</v>
+        <v>9.025946796836735</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3746789643846273</v>
+        <v>0.382555749950334</v>
       </c>
       <c r="T62">
-        <v>2.01138280577013</v>
+        <v>2.059556245750537</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.216107793013069</v>
+        <v>2.179778157062036</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1884990424806303</v>
+        <v>0.1884684992074097</v>
       </c>
       <c r="C63">
-        <v>36.36421236645555</v>
+        <v>35.56543880778436</v>
       </c>
       <c r="D63">
-        <v>82.80071236645554</v>
+        <v>82.81843880778436</v>
       </c>
       <c r="E63">
-        <v>39.8565</v>
+        <v>40.673</v>
       </c>
       <c r="F63">
-        <v>49.8065</v>
+        <v>50.623</v>
       </c>
       <c r="G63">
         <v>3.37</v>
@@ -6453,28 +6453,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M63">
-        <v>3.7753327</v>
+        <v>3.837223400000001</v>
       </c>
       <c r="N63">
-        <v>4.454055055102041</v>
+        <v>4.39216435510204</v>
       </c>
       <c r="O63">
-        <v>0.6681082582653061</v>
+        <v>0.6588246532653059</v>
       </c>
       <c r="P63">
-        <v>3.785946796836734</v>
+        <v>3.733339701836734</v>
       </c>
       <c r="Q63">
-        <v>9.025946796836735</v>
+        <v>8.973339701836734</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.382555749950334</v>
+        <v>0.3908471031773939</v>
       </c>
       <c r="T63">
-        <v>2.059556245750537</v>
+        <v>2.110265129940438</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.179778157062036</v>
+        <v>2.144620444851357</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1884684992074097</v>
+        <v>0.188437955934189</v>
       </c>
       <c r="C64">
-        <v>35.56543880778436</v>
+        <v>34.76667284069057</v>
       </c>
       <c r="D64">
-        <v>82.81843880778436</v>
+        <v>82.83617284069057</v>
       </c>
       <c r="E64">
-        <v>40.673</v>
+        <v>41.48950000000001</v>
       </c>
       <c r="F64">
-        <v>50.623</v>
+        <v>51.4395</v>
       </c>
       <c r="G64">
         <v>3.37</v>
@@ -6535,28 +6535,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M64">
-        <v>3.837223400000001</v>
+        <v>3.899114100000001</v>
       </c>
       <c r="N64">
-        <v>4.39216435510204</v>
+        <v>4.33027365510204</v>
       </c>
       <c r="O64">
-        <v>0.6588246532653059</v>
+        <v>0.649541048265306</v>
       </c>
       <c r="P64">
-        <v>3.733339701836734</v>
+        <v>3.680732606836734</v>
       </c>
       <c r="Q64">
-        <v>8.973339701836734</v>
+        <v>8.920732606836735</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3908471031773939</v>
+        <v>0.3995866376599704</v>
       </c>
       <c r="T64">
-        <v>2.110265129940438</v>
+        <v>2.163715034897361</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.144620444851357</v>
+        <v>2.110578850488638</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.188437955934189</v>
+        <v>0.1884074126609684</v>
       </c>
       <c r="C65">
-        <v>34.76667284069057</v>
+        <v>33.96791447005202</v>
       </c>
       <c r="D65">
-        <v>82.83617284069057</v>
+        <v>82.85391447005202</v>
       </c>
       <c r="E65">
-        <v>41.48950000000001</v>
+        <v>42.30600000000001</v>
       </c>
       <c r="F65">
-        <v>51.4395</v>
+        <v>52.25600000000001</v>
       </c>
       <c r="G65">
         <v>3.37</v>
@@ -6617,28 +6617,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M65">
-        <v>3.899114100000001</v>
+        <v>3.961004800000001</v>
       </c>
       <c r="N65">
-        <v>4.33027365510204</v>
+        <v>4.268382955102039</v>
       </c>
       <c r="O65">
-        <v>0.649541048265306</v>
+        <v>0.6402574432653059</v>
       </c>
       <c r="P65">
-        <v>3.680732606836734</v>
+        <v>3.628125511836733</v>
       </c>
       <c r="Q65">
-        <v>8.920732606836735</v>
+        <v>8.868125511836734</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3995866376599704</v>
+        <v>0.4088117018360233</v>
       </c>
       <c r="T65">
-        <v>2.163715034897361</v>
+        <v>2.220134379018557</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.110578850488638</v>
+        <v>2.077601055949752</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1884074126609684</v>
+        <v>0.1883768693877477</v>
       </c>
       <c r="C66">
-        <v>33.96791447005202</v>
+        <v>33.1691637007507</v>
       </c>
       <c r="D66">
-        <v>82.85391447005202</v>
+        <v>82.8716637007507</v>
       </c>
       <c r="E66">
-        <v>42.30600000000001</v>
+        <v>43.1225</v>
       </c>
       <c r="F66">
-        <v>52.25600000000001</v>
+        <v>53.07250000000001</v>
       </c>
       <c r="G66">
         <v>3.37</v>
@@ -6699,28 +6699,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M66">
-        <v>3.961004800000001</v>
+        <v>4.022895500000001</v>
       </c>
       <c r="N66">
-        <v>4.268382955102039</v>
+        <v>4.20649225510204</v>
       </c>
       <c r="O66">
-        <v>0.6402574432653059</v>
+        <v>0.630973838265306</v>
       </c>
       <c r="P66">
-        <v>3.628125511836733</v>
+        <v>3.575518416836734</v>
       </c>
       <c r="Q66">
-        <v>8.868125511836734</v>
+        <v>8.815518416836735</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4088117018360233</v>
+        <v>0.4185639125364222</v>
       </c>
       <c r="T66">
-        <v>2.220134379018557</v>
+        <v>2.279777685660965</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.077601055949752</v>
+        <v>2.045637962781295</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1883768693877477</v>
+        <v>0.1883463261145271</v>
       </c>
       <c r="C67">
-        <v>33.1691637007507</v>
+        <v>32.37042053767276</v>
       </c>
       <c r="D67">
-        <v>82.8716637007507</v>
+        <v>82.88942053767276</v>
       </c>
       <c r="E67">
-        <v>43.1225</v>
+        <v>43.93900000000001</v>
       </c>
       <c r="F67">
-        <v>53.07250000000001</v>
+        <v>53.889</v>
       </c>
       <c r="G67">
         <v>3.37</v>
@@ -6781,28 +6781,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M67">
-        <v>4.022895500000001</v>
+        <v>4.084786200000001</v>
       </c>
       <c r="N67">
-        <v>4.20649225510204</v>
+        <v>4.14460155510204</v>
       </c>
       <c r="O67">
-        <v>0.630973838265306</v>
+        <v>0.6216902332653059</v>
       </c>
       <c r="P67">
-        <v>3.575518416836734</v>
+        <v>3.522911321836734</v>
       </c>
       <c r="Q67">
-        <v>8.815518416836735</v>
+        <v>8.762911321836734</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4185639125364222</v>
+        <v>0.4288897826897857</v>
       </c>
       <c r="T67">
-        <v>2.279777685660965</v>
+        <v>2.342929422105867</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.045637962781295</v>
+        <v>2.014643448193699</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1883463261145271</v>
+        <v>0.1964026828413065</v>
       </c>
       <c r="C68">
-        <v>32.37042053767276</v>
+        <v>27.11982462298591</v>
       </c>
       <c r="D68">
-        <v>82.88942053767276</v>
+        <v>78.45532462298591</v>
       </c>
       <c r="E68">
-        <v>43.93900000000001</v>
+        <v>44.75550000000001</v>
       </c>
       <c r="F68">
-        <v>53.889</v>
+        <v>54.70550000000001</v>
       </c>
       <c r="G68">
         <v>3.37</v>
@@ -6863,45 +6863,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M68">
-        <v>4.084786200000001</v>
+        <v>4.923495000000001</v>
       </c>
       <c r="N68">
-        <v>4.14460155510204</v>
+        <v>3.30589275510204</v>
       </c>
       <c r="O68">
-        <v>0.6216902332653059</v>
+        <v>0.4958839132653059</v>
       </c>
       <c r="P68">
-        <v>3.522911321836734</v>
+        <v>2.810008841836733</v>
       </c>
       <c r="Q68">
-        <v>8.762911321836734</v>
+        <v>8.050008841836734</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4288897826897857</v>
+        <v>0.4398414631554742</v>
       </c>
       <c r="T68">
-        <v>2.342929422105867</v>
+        <v>2.409908536517126</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.15</v>
       </c>
       <c r="W68">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.014643448193699</v>
+        <v>1.671452444879509</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1964026828413065</v>
+        <v>0.1964928395680859</v>
       </c>
       <c r="C69">
-        <v>27.11982462298591</v>
+        <v>26.25638625957926</v>
       </c>
       <c r="D69">
-        <v>78.45532462298591</v>
+        <v>78.40838625957926</v>
       </c>
       <c r="E69">
-        <v>44.75550000000001</v>
+        <v>45.572</v>
       </c>
       <c r="F69">
-        <v>54.70550000000001</v>
+        <v>55.52200000000001</v>
       </c>
       <c r="G69">
         <v>3.37</v>
@@ -6945,28 +6945,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M69">
-        <v>4.923495000000001</v>
+        <v>4.996980000000001</v>
       </c>
       <c r="N69">
-        <v>3.30589275510204</v>
+        <v>3.23240775510204</v>
       </c>
       <c r="O69">
-        <v>0.4958839132653059</v>
+        <v>0.4848611632653059</v>
       </c>
       <c r="P69">
-        <v>2.810008841836733</v>
+        <v>2.747546591836734</v>
       </c>
       <c r="Q69">
-        <v>8.050008841836734</v>
+        <v>7.987546591836734</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4398414631554742</v>
+        <v>0.4514776236502684</v>
       </c>
       <c r="T69">
-        <v>2.409908536517126</v>
+        <v>2.48107384557909</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.671452444879509</v>
+        <v>1.646872261866575</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1964928395680859</v>
+        <v>0.1965829962948652</v>
       </c>
       <c r="C70">
-        <v>26.25638625957926</v>
+        <v>25.39300402729235</v>
       </c>
       <c r="D70">
-        <v>78.40838625957926</v>
+        <v>78.36150402729236</v>
       </c>
       <c r="E70">
-        <v>45.572</v>
+        <v>46.38850000000001</v>
       </c>
       <c r="F70">
-        <v>55.52200000000001</v>
+        <v>56.33850000000001</v>
       </c>
       <c r="G70">
         <v>3.37</v>
@@ -7027,28 +7027,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M70">
-        <v>4.996980000000001</v>
+        <v>5.070465</v>
       </c>
       <c r="N70">
-        <v>3.23240775510204</v>
+        <v>3.15892275510204</v>
       </c>
       <c r="O70">
-        <v>0.4848611632653059</v>
+        <v>0.473838413265306</v>
       </c>
       <c r="P70">
-        <v>2.747546591836734</v>
+        <v>2.685084341836734</v>
       </c>
       <c r="Q70">
-        <v>7.987546591836734</v>
+        <v>7.925084341836734</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4514776236502684</v>
+        <v>0.4638645041769847</v>
       </c>
       <c r="T70">
-        <v>2.48107384557909</v>
+        <v>2.556830464903116</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.646872261866575</v>
+        <v>1.62300454792648</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1965829962948652</v>
+        <v>0.1966731530216446</v>
       </c>
       <c r="C71">
-        <v>25.39300402729235</v>
+        <v>24.52967782549887</v>
       </c>
       <c r="D71">
-        <v>78.36150402729236</v>
+        <v>78.31467782549888</v>
       </c>
       <c r="E71">
-        <v>46.38850000000001</v>
+        <v>47.20500000000001</v>
       </c>
       <c r="F71">
-        <v>56.33850000000001</v>
+        <v>57.15500000000001</v>
       </c>
       <c r="G71">
         <v>3.37</v>
@@ -7109,28 +7109,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M71">
-        <v>5.070465</v>
+        <v>5.14395</v>
       </c>
       <c r="N71">
-        <v>3.15892275510204</v>
+        <v>3.08543775510204</v>
       </c>
       <c r="O71">
-        <v>0.473838413265306</v>
+        <v>0.462815663265306</v>
       </c>
       <c r="P71">
-        <v>2.685084341836734</v>
+        <v>2.622622091836734</v>
       </c>
       <c r="Q71">
-        <v>7.925084341836734</v>
+        <v>7.862622091836735</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4638645041769847</v>
+        <v>0.4770771767388154</v>
       </c>
       <c r="T71">
-        <v>2.556830464903116</v>
+        <v>2.63763752551541</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.62300454792648</v>
+        <v>1.599818768670388</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1966731530216446</v>
+        <v>0.196763309748424</v>
       </c>
       <c r="C72">
-        <v>24.52967782549887</v>
+        <v>23.66640755381301</v>
       </c>
       <c r="D72">
-        <v>78.31467782549888</v>
+        <v>78.26790755381302</v>
       </c>
       <c r="E72">
-        <v>47.20500000000001</v>
+        <v>48.02150000000002</v>
       </c>
       <c r="F72">
-        <v>57.15500000000001</v>
+        <v>57.97150000000001</v>
       </c>
       <c r="G72">
         <v>3.37</v>
@@ -7191,28 +7191,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M72">
-        <v>5.14395</v>
+        <v>5.217435000000001</v>
       </c>
       <c r="N72">
-        <v>3.08543775510204</v>
+        <v>3.01195275510204</v>
       </c>
       <c r="O72">
-        <v>0.462815663265306</v>
+        <v>0.4517929132653059</v>
       </c>
       <c r="P72">
-        <v>2.622622091836734</v>
+        <v>2.560159841836734</v>
       </c>
       <c r="Q72">
-        <v>7.862622091836735</v>
+        <v>7.800159841836734</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4770771767388154</v>
+        <v>0.4912010680980138</v>
       </c>
       <c r="T72">
-        <v>2.63763752551541</v>
+        <v>2.724017486859587</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.599818768670388</v>
+        <v>1.57728610995672</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.196763309748424</v>
+        <v>0.1968534664752033</v>
       </c>
       <c r="C73">
-        <v>23.66640755381302</v>
+        <v>22.80319311208866</v>
       </c>
       <c r="D73">
-        <v>78.26790755381302</v>
+        <v>78.22119311208866</v>
       </c>
       <c r="E73">
-        <v>48.0215</v>
+        <v>48.83800000000001</v>
       </c>
       <c r="F73">
-        <v>57.9715</v>
+        <v>58.788</v>
       </c>
       <c r="G73">
         <v>3.37</v>
@@ -7273,28 +7273,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M73">
-        <v>5.217435</v>
+        <v>5.29092</v>
       </c>
       <c r="N73">
-        <v>3.01195275510204</v>
+        <v>2.938467755102041</v>
       </c>
       <c r="O73">
-        <v>0.451792913265306</v>
+        <v>0.4407701632653061</v>
       </c>
       <c r="P73">
-        <v>2.560159841836734</v>
+        <v>2.497697591836734</v>
       </c>
       <c r="Q73">
-        <v>7.800159841836734</v>
+        <v>7.737697591836735</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4912010680980137</v>
+        <v>0.5063338088400118</v>
       </c>
       <c r="T73">
-        <v>2.724017486859586</v>
+        <v>2.816567445442632</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.57728610995672</v>
+        <v>1.555379358429544</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1968534664752033</v>
+        <v>0.1969436232019827</v>
       </c>
       <c r="C74">
-        <v>22.80319311208866</v>
+        <v>21.9400344004185</v>
       </c>
       <c r="D74">
-        <v>78.22119311208866</v>
+        <v>78.17453440041849</v>
       </c>
       <c r="E74">
-        <v>48.83800000000001</v>
+        <v>49.6545</v>
       </c>
       <c r="F74">
-        <v>58.788</v>
+        <v>59.6045</v>
       </c>
       <c r="G74">
         <v>3.37</v>
@@ -7355,28 +7355,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M74">
-        <v>5.29092</v>
+        <v>5.364405</v>
       </c>
       <c r="N74">
-        <v>2.938467755102041</v>
+        <v>2.864982755102041</v>
       </c>
       <c r="O74">
-        <v>0.4407701632653061</v>
+        <v>0.4297474132653061</v>
       </c>
       <c r="P74">
-        <v>2.497697591836734</v>
+        <v>2.435235341836735</v>
       </c>
       <c r="Q74">
-        <v>7.737697591836735</v>
+        <v>7.675235341836735</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5063338088400118</v>
+        <v>0.5225874933406766</v>
       </c>
       <c r="T74">
-        <v>2.816567445442632</v>
+        <v>2.915972956513311</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.555379358429544</v>
+        <v>1.534072791875714</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1969436232019827</v>
+        <v>0.197033779928762</v>
       </c>
       <c r="C75">
-        <v>21.9400344004185</v>
+        <v>21.07693131913361</v>
       </c>
       <c r="D75">
-        <v>78.17453440041849</v>
+        <v>78.12793131913361</v>
       </c>
       <c r="E75">
-        <v>49.6545</v>
+        <v>50.471</v>
       </c>
       <c r="F75">
-        <v>59.6045</v>
+        <v>60.42100000000001</v>
       </c>
       <c r="G75">
         <v>3.37</v>
@@ -7437,28 +7437,28 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M75">
-        <v>5.364405</v>
+        <v>5.43789</v>
       </c>
       <c r="N75">
-        <v>2.864982755102041</v>
+        <v>2.79149775510204</v>
       </c>
       <c r="O75">
-        <v>0.4297474132653061</v>
+        <v>0.418724663265306</v>
       </c>
       <c r="P75">
-        <v>2.435235341836735</v>
+        <v>2.372773091836734</v>
       </c>
       <c r="Q75">
-        <v>7.675235341836735</v>
+        <v>7.612773091836734</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5225874933406766</v>
+        <v>0.5400914612644694</v>
       </c>
       <c r="T75">
-        <v>2.915972956513311</v>
+        <v>3.023025045358658</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.534072791875714</v>
+        <v>1.513342078471988</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.197033779928762</v>
+        <v>0.2361060704530637</v>
       </c>
       <c r="C76">
-        <v>21.07693131913361</v>
+        <v>4.219759451460497</v>
       </c>
       <c r="D76">
-        <v>78.12793131913361</v>
+        <v>62.0872594514605</v>
       </c>
       <c r="E76">
-        <v>50.471</v>
+        <v>51.28750000000001</v>
       </c>
       <c r="F76">
-        <v>60.42100000000001</v>
+        <v>61.2375</v>
       </c>
       <c r="G76">
         <v>3.37</v>
@@ -7519,45 +7519,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M76">
-        <v>5.43789</v>
+        <v>8.989665000000002</v>
       </c>
       <c r="N76">
-        <v>2.79149775510204</v>
+        <v>-0.7602772448979618</v>
       </c>
       <c r="O76">
-        <v>0.418724663265306</v>
+        <v>-0.1140415867346943</v>
       </c>
       <c r="P76">
-        <v>2.372773091836734</v>
+        <v>-0.6462356581632676</v>
       </c>
       <c r="Q76">
-        <v>7.612773091836734</v>
+        <v>4.593764341836732</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5400914612644694</v>
+        <v>0.5644974312679953</v>
       </c>
       <c r="T76">
-        <v>3.023025045358658</v>
+        <v>3.172288919729847</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.15</v>
+        <v>0.1373141449948697</v>
       </c>
       <c r="W76">
-        <v>0.0765</v>
+        <v>0.1266422835147532</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.513342078471988</v>
+        <v>0.9154276332991317</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2361060704530637</v>
+        <v>0.2371160704530637</v>
       </c>
       <c r="C77">
-        <v>4.219759451460497</v>
+        <v>3.075487028069873</v>
       </c>
       <c r="D77">
-        <v>62.0872594514605</v>
+        <v>61.75948702806987</v>
       </c>
       <c r="E77">
-        <v>51.28750000000001</v>
+        <v>52.104</v>
       </c>
       <c r="F77">
-        <v>61.2375</v>
+        <v>62.054</v>
       </c>
       <c r="G77">
         <v>3.37</v>
@@ -7601,37 +7601,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M77">
-        <v>8.989665000000002</v>
+        <v>9.1095272</v>
       </c>
       <c r="N77">
-        <v>-0.7602772448979618</v>
+        <v>-0.88013944489796</v>
       </c>
       <c r="O77">
-        <v>-0.1140415867346943</v>
+        <v>-0.132020916734694</v>
       </c>
       <c r="P77">
-        <v>-0.6462356581632676</v>
+        <v>-0.7481185281632661</v>
       </c>
       <c r="Q77">
-        <v>4.593764341836732</v>
+        <v>4.491881471836734</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5644974312679953</v>
+        <v>0.5861098242374951</v>
       </c>
       <c r="T77">
-        <v>3.172288919729847</v>
+        <v>3.30446762471859</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1373141449948697</v>
+        <v>0.1355073799291478</v>
       </c>
       <c r="W77">
-        <v>0.1266422835147532</v>
+        <v>0.1269075166264011</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9154276332991317</v>
+        <v>0.9033825328609854</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2371160704530637</v>
+        <v>0.2381260704530637</v>
       </c>
       <c r="C78">
-        <v>3.075487028069873</v>
+        <v>1.934657197218499</v>
       </c>
       <c r="D78">
-        <v>61.75948702806987</v>
+        <v>61.4351571972185</v>
       </c>
       <c r="E78">
-        <v>52.104</v>
+        <v>52.9205</v>
       </c>
       <c r="F78">
-        <v>62.054</v>
+        <v>62.87050000000001</v>
       </c>
       <c r="G78">
         <v>3.37</v>
@@ -7683,37 +7683,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M78">
-        <v>9.1095272</v>
+        <v>9.229389400000002</v>
       </c>
       <c r="N78">
-        <v>-0.88013944489796</v>
+        <v>-1.000001644897962</v>
       </c>
       <c r="O78">
-        <v>-0.132020916734694</v>
+        <v>-0.1500002467346943</v>
       </c>
       <c r="P78">
-        <v>-0.7481185281632661</v>
+        <v>-0.8500013981632676</v>
       </c>
       <c r="Q78">
-        <v>4.491881471836734</v>
+        <v>4.389998601836733</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5861098242374951</v>
+        <v>0.6096015557260819</v>
       </c>
       <c r="T78">
-        <v>3.30446762471859</v>
+        <v>3.448140130141137</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1355073799291478</v>
+        <v>0.1337475438261718</v>
       </c>
       <c r="W78">
-        <v>0.1269075166264011</v>
+        <v>0.127165860566318</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9033825328609854</v>
+        <v>0.8916502921744789</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2381260704530637</v>
+        <v>0.2391360704530636</v>
       </c>
       <c r="C79">
-        <v>1.934657197218499</v>
+        <v>0.7972160059354465</v>
       </c>
       <c r="D79">
-        <v>61.4351571972185</v>
+        <v>61.11421600593545</v>
       </c>
       <c r="E79">
-        <v>52.9205</v>
+        <v>53.73700000000001</v>
       </c>
       <c r="F79">
-        <v>62.87050000000001</v>
+        <v>63.687</v>
       </c>
       <c r="G79">
         <v>3.37</v>
@@ -7765,37 +7765,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M79">
-        <v>9.229389400000002</v>
+        <v>9.349251600000002</v>
       </c>
       <c r="N79">
-        <v>-1.000001644897962</v>
+        <v>-1.119863844897962</v>
       </c>
       <c r="O79">
-        <v>-0.1500002467346943</v>
+        <v>-0.1679795767346943</v>
       </c>
       <c r="P79">
-        <v>-0.8500013981632676</v>
+        <v>-0.9518842681632675</v>
       </c>
       <c r="Q79">
-        <v>4.389998601836733</v>
+        <v>4.288115731836733</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6096015557260819</v>
+        <v>0.6352288991681764</v>
       </c>
       <c r="T79">
-        <v>3.448140130141137</v>
+        <v>3.60487377242028</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1337475438261718</v>
+        <v>0.1320328317258363</v>
       </c>
       <c r="W79">
-        <v>0.127165860566318</v>
+        <v>0.1274175803026472</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8916502921744789</v>
+        <v>0.880218878172242</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2391360704530636</v>
+        <v>0.2401460704530637</v>
       </c>
       <c r="C80">
-        <v>0.7972160059354465</v>
+        <v>-0.3368893771942538</v>
       </c>
       <c r="D80">
-        <v>61.11421600593545</v>
+        <v>60.79661062280575</v>
       </c>
       <c r="E80">
-        <v>53.73700000000001</v>
+        <v>54.5535</v>
       </c>
       <c r="F80">
-        <v>63.687</v>
+        <v>64.5035</v>
       </c>
       <c r="G80">
         <v>3.37</v>
@@ -7847,37 +7847,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M80">
-        <v>9.349251600000002</v>
+        <v>9.469113800000001</v>
       </c>
       <c r="N80">
-        <v>-1.119863844897962</v>
+        <v>-1.23972604489796</v>
       </c>
       <c r="O80">
-        <v>-0.1679795767346943</v>
+        <v>-0.185958906734694</v>
       </c>
       <c r="P80">
-        <v>-0.9518842681632675</v>
+        <v>-1.053767138163266</v>
       </c>
       <c r="Q80">
-        <v>4.288115731836733</v>
+        <v>4.186232861836734</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6352288991681764</v>
+        <v>0.6632969419857089</v>
       </c>
       <c r="T80">
-        <v>3.60487377242028</v>
+        <v>3.776534428249818</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1320328317258363</v>
+        <v>0.1303615300584207</v>
       </c>
       <c r="W80">
-        <v>0.1274175803026472</v>
+        <v>0.1276629273874239</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.880218878172242</v>
+        <v>0.8690768670561378</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2401460704530637</v>
+        <v>0.2411560704530637</v>
       </c>
       <c r="C81">
-        <v>-0.3368893771942538</v>
+        <v>-1.467710691022006</v>
       </c>
       <c r="D81">
-        <v>60.79661062280575</v>
+        <v>60.482289308978</v>
       </c>
       <c r="E81">
-        <v>54.5535</v>
+        <v>55.37</v>
       </c>
       <c r="F81">
-        <v>64.5035</v>
+        <v>65.32000000000001</v>
       </c>
       <c r="G81">
         <v>3.37</v>
@@ -7929,37 +7929,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M81">
-        <v>9.469113800000001</v>
+        <v>9.588976000000002</v>
       </c>
       <c r="N81">
-        <v>-1.23972604489796</v>
+        <v>-1.359588244897962</v>
       </c>
       <c r="O81">
-        <v>-0.185958906734694</v>
+        <v>-0.2039382367346943</v>
       </c>
       <c r="P81">
-        <v>-1.053767138163266</v>
+        <v>-1.155650008163268</v>
       </c>
       <c r="Q81">
-        <v>4.186232861836734</v>
+        <v>4.084349991836732</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6632969419857089</v>
+        <v>0.6941717890849942</v>
       </c>
       <c r="T81">
-        <v>3.776534428249818</v>
+        <v>3.965361149662308</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1303615300584207</v>
+        <v>0.1287320109326904</v>
       </c>
       <c r="W81">
-        <v>0.1276629273874239</v>
+        <v>0.1279021407950811</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8690768670561378</v>
+        <v>0.858213406217936</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2411560704530637</v>
+        <v>0.2421660704530637</v>
       </c>
       <c r="C82">
-        <v>-1.467710691022006</v>
+        <v>-2.595298609933479</v>
       </c>
       <c r="D82">
-        <v>60.482289308978</v>
+        <v>60.17120139006654</v>
       </c>
       <c r="E82">
-        <v>55.37</v>
+        <v>56.18650000000001</v>
       </c>
       <c r="F82">
-        <v>65.32000000000001</v>
+        <v>66.13650000000001</v>
       </c>
       <c r="G82">
         <v>3.37</v>
@@ -8011,37 +8011,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M82">
-        <v>9.588976000000002</v>
+        <v>9.708838200000002</v>
       </c>
       <c r="N82">
-        <v>-1.359588244897962</v>
+        <v>-1.479450444897962</v>
       </c>
       <c r="O82">
-        <v>-0.2039382367346943</v>
+        <v>-0.2219175667346943</v>
       </c>
       <c r="P82">
-        <v>-1.155650008163268</v>
+        <v>-1.257532878163268</v>
       </c>
       <c r="Q82">
-        <v>4.084349991836732</v>
+        <v>3.982467121836732</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6941717890849942</v>
+        <v>0.7282966200894676</v>
       </c>
       <c r="T82">
-        <v>3.965361149662308</v>
+        <v>4.174064368065588</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1287320109326904</v>
+        <v>0.1271427268471016</v>
       </c>
       <c r="W82">
-        <v>0.1279021407950811</v>
+        <v>0.1281354476988455</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.858213406217936</v>
+        <v>0.8476181789806775</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2421660704530637</v>
+        <v>0.2431760704530637</v>
       </c>
       <c r="C83">
-        <v>-2.595298609933479</v>
+        <v>-3.719702771083639</v>
       </c>
       <c r="D83">
-        <v>60.17120139006654</v>
+        <v>59.86329722891637</v>
       </c>
       <c r="E83">
-        <v>56.18650000000001</v>
+        <v>57.003</v>
       </c>
       <c r="F83">
-        <v>66.13650000000001</v>
+        <v>66.953</v>
       </c>
       <c r="G83">
         <v>3.37</v>
@@ -8093,37 +8093,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M83">
-        <v>9.708838200000002</v>
+        <v>9.828700400000001</v>
       </c>
       <c r="N83">
-        <v>-1.479450444897962</v>
+        <v>-1.59931264489796</v>
       </c>
       <c r="O83">
-        <v>-0.2219175667346943</v>
+        <v>-0.239896896734694</v>
       </c>
       <c r="P83">
-        <v>-1.257532878163268</v>
+        <v>-1.359415748163266</v>
       </c>
       <c r="Q83">
-        <v>3.982467121836732</v>
+        <v>3.880584251836734</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7282966200894676</v>
+        <v>0.7662130989833269</v>
       </c>
       <c r="T83">
-        <v>4.174064368065588</v>
+        <v>4.405956832958121</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1271427268471016</v>
+        <v>0.1255922057879907</v>
       </c>
       <c r="W83">
-        <v>0.1281354476988455</v>
+        <v>0.128363064190323</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8476181789806775</v>
+        <v>0.8372813719199377</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2431760704530637</v>
+        <v>0.2441860704530637</v>
       </c>
       <c r="C84">
-        <v>-3.719702771083639</v>
+        <v>-4.840971800799927</v>
       </c>
       <c r="D84">
-        <v>59.86329722891637</v>
+        <v>59.55852819920008</v>
       </c>
       <c r="E84">
-        <v>57.003</v>
+        <v>57.81950000000001</v>
       </c>
       <c r="F84">
-        <v>66.953</v>
+        <v>67.76950000000001</v>
       </c>
       <c r="G84">
         <v>3.37</v>
@@ -8175,37 +8175,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M84">
-        <v>9.828700400000001</v>
+        <v>9.948562600000002</v>
       </c>
       <c r="N84">
-        <v>-1.59931264489796</v>
+        <v>-1.719174844897962</v>
       </c>
       <c r="O84">
-        <v>-0.239896896734694</v>
+        <v>-0.2578762267346943</v>
       </c>
       <c r="P84">
-        <v>-1.359415748163266</v>
+        <v>-1.461298618163268</v>
       </c>
       <c r="Q84">
-        <v>3.880584251836734</v>
+        <v>3.778701381836733</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7662130989833269</v>
+        <v>0.8085903400999933</v>
       </c>
       <c r="T84">
-        <v>4.405956832958121</v>
+        <v>4.665130764308599</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1255922057879907</v>
+        <v>0.1240790466821112</v>
       </c>
       <c r="W84">
-        <v>0.128363064190323</v>
+        <v>0.1285851959470661</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8372813719199377</v>
+        <v>0.8271936445474082</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2441860704530637</v>
+        <v>0.2451960704530636</v>
       </c>
       <c r="C85">
-        <v>-4.840971800799927</v>
+        <v>-5.959153340182866</v>
       </c>
       <c r="D85">
-        <v>59.55852819920008</v>
+        <v>59.25684665981715</v>
       </c>
       <c r="E85">
-        <v>57.81950000000001</v>
+        <v>58.63600000000001</v>
       </c>
       <c r="F85">
-        <v>67.76950000000001</v>
+        <v>68.58600000000001</v>
       </c>
       <c r="G85">
         <v>3.37</v>
@@ -8257,37 +8257,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M85">
-        <v>9.948562600000002</v>
+        <v>10.0684248</v>
       </c>
       <c r="N85">
-        <v>-1.719174844897962</v>
+        <v>-1.839037044897962</v>
       </c>
       <c r="O85">
-        <v>-0.2578762267346943</v>
+        <v>-0.2758555567346943</v>
       </c>
       <c r="P85">
-        <v>-1.461298618163268</v>
+        <v>-1.563181488163268</v>
       </c>
       <c r="Q85">
-        <v>3.778701381836733</v>
+        <v>3.676818511836732</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8085903400999933</v>
+        <v>0.8562647363562429</v>
       </c>
       <c r="T85">
-        <v>4.665130764308599</v>
+        <v>4.956701437077887</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1240790466821112</v>
+        <v>0.1226019151739908</v>
       </c>
       <c r="W85">
-        <v>0.1285851959470661</v>
+        <v>0.1288020388524581</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8271936445474082</v>
+        <v>0.817346101159939</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2451960704530637</v>
+        <v>0.2462060704530637</v>
       </c>
       <c r="C86">
-        <v>-5.959153340182873</v>
+        <v>-7.074294069932797</v>
       </c>
       <c r="D86">
-        <v>59.25684665981713</v>
+        <v>58.95820593006721</v>
       </c>
       <c r="E86">
-        <v>58.636</v>
+        <v>59.4525</v>
       </c>
       <c r="F86">
-        <v>68.586</v>
+        <v>69.4025</v>
       </c>
       <c r="G86">
         <v>3.37</v>
@@ -8339,37 +8339,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M86">
-        <v>10.0684248</v>
+        <v>10.188287</v>
       </c>
       <c r="N86">
-        <v>-1.83903704489796</v>
+        <v>-1.95889924489796</v>
       </c>
       <c r="O86">
-        <v>-0.275855556734694</v>
+        <v>-0.293834886734694</v>
       </c>
       <c r="P86">
-        <v>-1.563181488163266</v>
+        <v>-1.665064358163266</v>
       </c>
       <c r="Q86">
-        <v>3.676818511836734</v>
+        <v>3.574935641836734</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8562647363562425</v>
+        <v>0.910295718779992</v>
       </c>
       <c r="T86">
-        <v>4.956701437077884</v>
+        <v>5.287148199549743</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1226019151739909</v>
+        <v>0.1211595397013557</v>
       </c>
       <c r="W86">
-        <v>0.1288020388524581</v>
+        <v>0.129013779571841</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8173461011599391</v>
+        <v>0.8077302646757045</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2462060704530637</v>
+        <v>0.2976597682310759</v>
       </c>
       <c r="C87">
-        <v>-7.074294069932797</v>
+        <v>-19.93566225497857</v>
       </c>
       <c r="D87">
-        <v>58.95820593006721</v>
+        <v>46.91333774502144</v>
       </c>
       <c r="E87">
-        <v>59.4525</v>
+        <v>60.26900000000001</v>
       </c>
       <c r="F87">
-        <v>69.4025</v>
+        <v>70.21900000000001</v>
       </c>
       <c r="G87">
         <v>3.37</v>
@@ -8421,45 +8421,45 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M87">
-        <v>10.188287</v>
+        <v>14.0999752</v>
       </c>
       <c r="N87">
-        <v>-1.95889924489796</v>
+        <v>-5.870587444897962</v>
       </c>
       <c r="O87">
-        <v>-0.293834886734694</v>
+        <v>-0.8805881167346944</v>
       </c>
       <c r="P87">
-        <v>-1.665064358163266</v>
+        <v>-4.989999328163268</v>
       </c>
       <c r="Q87">
-        <v>3.574935641836734</v>
+        <v>0.250000671836732</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.910295718779992</v>
+        <v>1.000643254250079</v>
       </c>
       <c r="T87">
-        <v>5.287148199549743</v>
+        <v>5.839702479597015</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1211595397013557</v>
+        <v>0.08754683222884717</v>
       </c>
       <c r="W87">
-        <v>0.129013779571841</v>
+        <v>0.1832205960884475</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8077302646757045</v>
+        <v>0.5836455481923144</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2976597682310759</v>
+        <v>0.2992097682310759</v>
       </c>
       <c r="C88">
-        <v>-19.93566225497857</v>
+        <v>-21.03911123098834</v>
       </c>
       <c r="D88">
-        <v>46.91333774502144</v>
+        <v>46.62638876901166</v>
       </c>
       <c r="E88">
-        <v>60.26900000000001</v>
+        <v>61.0855</v>
       </c>
       <c r="F88">
-        <v>70.21900000000001</v>
+        <v>71.0355</v>
       </c>
       <c r="G88">
         <v>3.37</v>
@@ -8503,37 +8503,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M88">
-        <v>14.0999752</v>
+        <v>14.2639284</v>
       </c>
       <c r="N88">
-        <v>-5.870587444897962</v>
+        <v>-6.034540644897961</v>
       </c>
       <c r="O88">
-        <v>-0.8805881167346944</v>
+        <v>-0.905181096734694</v>
       </c>
       <c r="P88">
-        <v>-4.989999328163268</v>
+        <v>-5.129359548163267</v>
       </c>
       <c r="Q88">
-        <v>0.250000671836732</v>
+        <v>0.1106404518367334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.000643254250079</v>
+        <v>1.074092735346239</v>
       </c>
       <c r="T88">
-        <v>5.839702479597015</v>
+        <v>6.28891036264294</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08754683222884717</v>
+        <v>0.08654054680092939</v>
       </c>
       <c r="W88">
-        <v>0.1832205960884475</v>
+        <v>0.1834226582023734</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5836455481923144</v>
+        <v>0.5769369786728626</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2992097682310759</v>
+        <v>0.300759768231076</v>
       </c>
       <c r="C89">
-        <v>-21.03911123098834</v>
+        <v>-22.13907125722459</v>
       </c>
       <c r="D89">
-        <v>46.62638876901166</v>
+        <v>46.34292874277541</v>
       </c>
       <c r="E89">
-        <v>61.0855</v>
+        <v>61.902</v>
       </c>
       <c r="F89">
-        <v>71.0355</v>
+        <v>71.852</v>
       </c>
       <c r="G89">
         <v>3.37</v>
@@ -8585,37 +8585,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M89">
-        <v>14.2639284</v>
+        <v>14.4278816</v>
       </c>
       <c r="N89">
-        <v>-6.034540644897961</v>
+        <v>-6.198493844897961</v>
       </c>
       <c r="O89">
-        <v>-0.905181096734694</v>
+        <v>-0.929774076734694</v>
       </c>
       <c r="P89">
-        <v>-5.129359548163267</v>
+        <v>-5.268719768163266</v>
       </c>
       <c r="Q89">
-        <v>0.1106404518367334</v>
+        <v>-0.02871976816326605</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.074092735346239</v>
+        <v>1.159783796625093</v>
       </c>
       <c r="T89">
-        <v>6.28891036264294</v>
+        <v>6.81298622619652</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08654054680092939</v>
+        <v>0.08555713149637338</v>
       </c>
       <c r="W89">
-        <v>0.1834226582023734</v>
+        <v>0.1836201279955282</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5769369786728626</v>
+        <v>0.5703808766424892</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.300759768231076</v>
+        <v>0.302309768231076</v>
       </c>
       <c r="C90">
-        <v>-22.13907125722459</v>
+        <v>-23.23560558124532</v>
       </c>
       <c r="D90">
-        <v>46.34292874277541</v>
+        <v>46.06289441875469</v>
       </c>
       <c r="E90">
-        <v>61.902</v>
+        <v>62.71850000000001</v>
       </c>
       <c r="F90">
-        <v>71.852</v>
+        <v>72.66850000000001</v>
       </c>
       <c r="G90">
         <v>3.37</v>
@@ -8667,37 +8667,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M90">
-        <v>14.4278816</v>
+        <v>14.5918348</v>
       </c>
       <c r="N90">
-        <v>-6.198493844897961</v>
+        <v>-6.362447044897962</v>
       </c>
       <c r="O90">
-        <v>-0.929774076734694</v>
+        <v>-0.9543670567346942</v>
       </c>
       <c r="P90">
-        <v>-5.268719768163266</v>
+        <v>-5.408079988163268</v>
       </c>
       <c r="Q90">
-        <v>-0.02871976816326605</v>
+        <v>-0.1680799881632673</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.159783796625093</v>
+        <v>1.261055050863738</v>
       </c>
       <c r="T90">
-        <v>6.81298622619652</v>
+        <v>7.432348610396204</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08555713149637338</v>
+        <v>0.08459581541214446</v>
       </c>
       <c r="W90">
-        <v>0.1836201279955282</v>
+        <v>0.1838131602652414</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5703808766424892</v>
+        <v>0.5639721027476297</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.302309768231076</v>
+        <v>0.303859768231076</v>
       </c>
       <c r="C91">
-        <v>-23.23560558124532</v>
+        <v>-24.32877593105801</v>
       </c>
       <c r="D91">
-        <v>46.06289441875469</v>
+        <v>45.786224068942</v>
       </c>
       <c r="E91">
-        <v>62.71850000000001</v>
+        <v>63.53500000000001</v>
       </c>
       <c r="F91">
-        <v>72.66850000000001</v>
+        <v>73.48500000000001</v>
       </c>
       <c r="G91">
         <v>3.37</v>
@@ -8749,37 +8749,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M91">
-        <v>14.5918348</v>
+        <v>14.755788</v>
       </c>
       <c r="N91">
-        <v>-6.362447044897962</v>
+        <v>-6.526400244897962</v>
       </c>
       <c r="O91">
-        <v>-0.9543670567346942</v>
+        <v>-0.9789600367346942</v>
       </c>
       <c r="P91">
-        <v>-5.408079988163268</v>
+        <v>-5.547440208163268</v>
       </c>
       <c r="Q91">
-        <v>-0.1680799881632673</v>
+        <v>-0.3074402081632677</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.261055050863738</v>
+        <v>1.382580555950111</v>
       </c>
       <c r="T91">
-        <v>7.432348610396204</v>
+        <v>8.175583471435823</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08459581541214446</v>
+        <v>0.08365586190756508</v>
       </c>
       <c r="W91">
-        <v>0.1838131602652414</v>
+        <v>0.1840019029289609</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5639721027476297</v>
+        <v>0.5577057460504338</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.303859768231076</v>
+        <v>0.3054097682310759</v>
       </c>
       <c r="C92">
-        <v>-24.32877593105801</v>
+        <v>-25.41864256048193</v>
       </c>
       <c r="D92">
-        <v>45.786224068942</v>
+        <v>45.51285743951808</v>
       </c>
       <c r="E92">
-        <v>63.53500000000001</v>
+        <v>64.3515</v>
       </c>
       <c r="F92">
-        <v>73.48500000000001</v>
+        <v>74.3015</v>
       </c>
       <c r="G92">
         <v>3.37</v>
@@ -8831,37 +8831,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M92">
-        <v>14.755788</v>
+        <v>14.9197412</v>
       </c>
       <c r="N92">
-        <v>-6.526400244897962</v>
+        <v>-6.69035344489796</v>
       </c>
       <c r="O92">
-        <v>-0.9789600367346942</v>
+        <v>-1.003553016734694</v>
       </c>
       <c r="P92">
-        <v>-5.547440208163268</v>
+        <v>-5.686800428163266</v>
       </c>
       <c r="Q92">
-        <v>-0.3074402081632677</v>
+        <v>-0.4468004281632663</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.382580555950111</v>
+        <v>1.531111728833457</v>
       </c>
       <c r="T92">
-        <v>8.175583471435823</v>
+        <v>9.083981634928694</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08365586190756508</v>
+        <v>0.08273656672176767</v>
       </c>
       <c r="W92">
-        <v>0.1840019029289609</v>
+        <v>0.1841864974022691</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5577057460504338</v>
+        <v>0.5515771114784511</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3054097682310759</v>
+        <v>0.306959768231076</v>
       </c>
       <c r="C93">
-        <v>-25.41864256048193</v>
+        <v>-26.50526429289532</v>
       </c>
       <c r="D93">
-        <v>45.51285743951808</v>
+        <v>45.24273570710469</v>
       </c>
       <c r="E93">
-        <v>64.3515</v>
+        <v>65.16800000000001</v>
       </c>
       <c r="F93">
-        <v>74.3015</v>
+        <v>75.11800000000001</v>
       </c>
       <c r="G93">
         <v>3.37</v>
@@ -8913,37 +8913,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M93">
-        <v>14.9197412</v>
+        <v>15.0836944</v>
       </c>
       <c r="N93">
-        <v>-6.69035344489796</v>
+        <v>-6.854306644897962</v>
       </c>
       <c r="O93">
-        <v>-1.003553016734694</v>
+        <v>-1.028145996734694</v>
       </c>
       <c r="P93">
-        <v>-5.686800428163266</v>
+        <v>-5.826160648163268</v>
       </c>
       <c r="Q93">
-        <v>-0.4468004281632663</v>
+        <v>-0.5861606481632675</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.531111728833457</v>
+        <v>1.71677569493764</v>
       </c>
       <c r="T93">
-        <v>9.083981634928694</v>
+        <v>10.21947933929478</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08273656672176767</v>
+        <v>0.08183725621392235</v>
       </c>
       <c r="W93">
-        <v>0.1841864974022691</v>
+        <v>0.1843670789522444</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5515771114784511</v>
+        <v>0.5455817080928157</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.306959768231076</v>
+        <v>0.308509768231076</v>
       </c>
       <c r="C94">
-        <v>-26.50526429289532</v>
+        <v>-27.58869856343349</v>
       </c>
       <c r="D94">
-        <v>45.24273570710469</v>
+        <v>44.97580143656653</v>
       </c>
       <c r="E94">
-        <v>65.16800000000001</v>
+        <v>65.98450000000001</v>
       </c>
       <c r="F94">
-        <v>75.11800000000001</v>
+        <v>75.93450000000001</v>
       </c>
       <c r="G94">
         <v>3.37</v>
@@ -8995,37 +8995,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M94">
-        <v>15.0836944</v>
+        <v>15.2476476</v>
       </c>
       <c r="N94">
-        <v>-6.854306644897962</v>
+        <v>-7.018259844897964</v>
       </c>
       <c r="O94">
-        <v>-1.028145996734694</v>
+        <v>-1.052738976734694</v>
       </c>
       <c r="P94">
-        <v>-5.826160648163268</v>
+        <v>-5.965520868163269</v>
       </c>
       <c r="Q94">
-        <v>-0.5861606481632675</v>
+        <v>-0.7255208681632688</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.71677569493764</v>
+        <v>1.95548650850016</v>
       </c>
       <c r="T94">
-        <v>10.21947933929478</v>
+        <v>11.67940495919404</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08183725621392235</v>
+        <v>0.08095728571699845</v>
       </c>
       <c r="W94">
-        <v>0.1843670789522444</v>
+        <v>0.1845437770280267</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5455817080928157</v>
+        <v>0.539715238113323</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.308509768231076</v>
+        <v>0.3100597682310759</v>
       </c>
       <c r="C95">
-        <v>-27.58869856343349</v>
+        <v>-28.66900145970227</v>
       </c>
       <c r="D95">
-        <v>44.97580143656653</v>
+        <v>44.71199854029774</v>
       </c>
       <c r="E95">
-        <v>65.98450000000001</v>
+        <v>66.801</v>
       </c>
       <c r="F95">
-        <v>75.93450000000001</v>
+        <v>76.751</v>
       </c>
       <c r="G95">
         <v>3.37</v>
@@ -9077,37 +9077,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M95">
-        <v>15.2476476</v>
+        <v>15.4116008</v>
       </c>
       <c r="N95">
-        <v>-7.018259844897964</v>
+        <v>-7.182213044897962</v>
       </c>
       <c r="O95">
-        <v>-1.052738976734694</v>
+        <v>-1.077331956734694</v>
       </c>
       <c r="P95">
-        <v>-5.965520868163269</v>
+        <v>-6.104881088163268</v>
       </c>
       <c r="Q95">
-        <v>-0.7255208681632688</v>
+        <v>-0.8648810881632674</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.95548650850016</v>
+        <v>2.273767593250187</v>
       </c>
       <c r="T95">
-        <v>11.67940495919404</v>
+        <v>13.62597245239305</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08095728571699845</v>
+        <v>0.08009603799660485</v>
       </c>
       <c r="W95">
-        <v>0.1845437770280267</v>
+        <v>0.1847167155702818</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.539715238113323</v>
+        <v>0.5339735866440325</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3100597682310759</v>
+        <v>0.311609768231076</v>
       </c>
       <c r="C96">
-        <v>-28.66900145970227</v>
+        <v>-29.74622776106685</v>
       </c>
       <c r="D96">
-        <v>44.71199854029774</v>
+        <v>44.45127223893316</v>
       </c>
       <c r="E96">
-        <v>66.801</v>
+        <v>67.61750000000001</v>
       </c>
       <c r="F96">
-        <v>76.751</v>
+        <v>77.56750000000001</v>
       </c>
       <c r="G96">
         <v>3.37</v>
@@ -9159,37 +9159,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M96">
-        <v>15.4116008</v>
+        <v>15.575554</v>
       </c>
       <c r="N96">
-        <v>-7.182213044897962</v>
+        <v>-7.346166244897962</v>
       </c>
       <c r="O96">
-        <v>-1.077331956734694</v>
+        <v>-1.101924936734694</v>
       </c>
       <c r="P96">
-        <v>-6.104881088163268</v>
+        <v>-6.244241308163268</v>
       </c>
       <c r="Q96">
-        <v>-0.8648810881632674</v>
+        <v>-1.004241308163268</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.273767593250187</v>
+        <v>2.719361111900226</v>
       </c>
       <c r="T96">
-        <v>13.62597245239305</v>
+        <v>16.35116694287167</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08009603799660485</v>
+        <v>0.07925292180716691</v>
       </c>
       <c r="W96">
-        <v>0.1847167155702818</v>
+        <v>0.1848860133011209</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5339735866440325</v>
+        <v>0.5283528120477794</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.311609768231076</v>
+        <v>0.3131597682310759</v>
       </c>
       <c r="C97">
-        <v>-29.74622776106685</v>
+        <v>-30.82043097657381</v>
       </c>
       <c r="D97">
-        <v>44.45127223893316</v>
+        <v>44.19356902342621</v>
       </c>
       <c r="E97">
-        <v>67.61750000000001</v>
+        <v>68.43400000000001</v>
       </c>
       <c r="F97">
-        <v>77.56750000000001</v>
+        <v>78.38400000000001</v>
       </c>
       <c r="G97">
         <v>3.37</v>
@@ -9241,37 +9241,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M97">
-        <v>15.575554</v>
+        <v>15.7395072</v>
       </c>
       <c r="N97">
-        <v>-7.346166244897962</v>
+        <v>-7.510119444897963</v>
       </c>
       <c r="O97">
-        <v>-1.101924936734694</v>
+        <v>-1.126517916734694</v>
       </c>
       <c r="P97">
-        <v>-6.244241308163268</v>
+        <v>-6.383601528163269</v>
       </c>
       <c r="Q97">
-        <v>-1.004241308163268</v>
+        <v>-1.143601528163269</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.719361111900226</v>
+        <v>3.387751389875283</v>
       </c>
       <c r="T97">
-        <v>16.35116694287167</v>
+        <v>20.43895867858959</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07925292180716691</v>
+        <v>0.07842737053834226</v>
       </c>
       <c r="W97">
-        <v>0.1848860133011209</v>
+        <v>0.1850517839959009</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5283528120477794</v>
+        <v>0.5228491369222816</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3131597682310759</v>
+        <v>0.3147097682310759</v>
       </c>
       <c r="C98">
-        <v>-30.8204309765738</v>
+        <v>-31.89166338156196</v>
       </c>
       <c r="D98">
-        <v>44.19356902342621</v>
+        <v>43.93883661843805</v>
       </c>
       <c r="E98">
-        <v>68.434</v>
+        <v>69.2505</v>
       </c>
       <c r="F98">
-        <v>78.384</v>
+        <v>79.20050000000001</v>
       </c>
       <c r="G98">
         <v>3.37</v>
@@ -9323,37 +9323,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M98">
-        <v>15.7395072</v>
+        <v>15.9034604</v>
       </c>
       <c r="N98">
-        <v>-7.51011944489796</v>
+        <v>-7.674072644897961</v>
       </c>
       <c r="O98">
-        <v>-1.126517916734694</v>
+        <v>-1.151110896734694</v>
       </c>
       <c r="P98">
-        <v>-6.383601528163266</v>
+        <v>-6.522961748163267</v>
       </c>
       <c r="Q98">
-        <v>-1.143601528163265</v>
+        <v>-1.282961748163267</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.387751389875274</v>
+        <v>4.501735186500366</v>
       </c>
       <c r="T98">
-        <v>20.43895867858954</v>
+        <v>27.25194490478605</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07842737053834227</v>
+        <v>0.07761884094516347</v>
       </c>
       <c r="W98">
-        <v>0.1850517839959009</v>
+        <v>0.1852141367382112</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5228491369222819</v>
+        <v>0.5174589396344231</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3147097682310759</v>
+        <v>0.3162597682310759</v>
       </c>
       <c r="C99">
-        <v>-31.89166338156196</v>
+        <v>-32.95997605301405</v>
       </c>
       <c r="D99">
-        <v>43.93883661843805</v>
+        <v>43.68702394698596</v>
       </c>
       <c r="E99">
-        <v>69.2505</v>
+        <v>70.06700000000001</v>
       </c>
       <c r="F99">
-        <v>79.20050000000001</v>
+        <v>80.01700000000001</v>
       </c>
       <c r="G99">
         <v>3.37</v>
@@ -9405,37 +9405,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M99">
-        <v>15.9034604</v>
+        <v>16.0674136</v>
       </c>
       <c r="N99">
-        <v>-7.674072644897961</v>
+        <v>-7.838025844897961</v>
       </c>
       <c r="O99">
-        <v>-1.151110896734694</v>
+        <v>-1.175703876734694</v>
       </c>
       <c r="P99">
-        <v>-6.522961748163267</v>
+        <v>-6.662321968163267</v>
       </c>
       <c r="Q99">
-        <v>-1.282961748163267</v>
+        <v>-1.422321968163267</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.501735186500366</v>
+        <v>6.729702779750548</v>
       </c>
       <c r="T99">
-        <v>27.25194490478605</v>
+        <v>40.87791735717907</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07761884094516347</v>
+        <v>0.07682681195592711</v>
       </c>
       <c r="W99">
-        <v>0.1852141367382112</v>
+        <v>0.1853731761592498</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5174589396344231</v>
+        <v>0.5121787463728474</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3162597682310759</v>
+        <v>0.317809768231076</v>
       </c>
       <c r="C100">
-        <v>-32.95997605301405</v>
+        <v>-34.02541890369985</v>
       </c>
       <c r="D100">
-        <v>43.68702394698596</v>
+        <v>43.43808109630015</v>
       </c>
       <c r="E100">
-        <v>70.06700000000001</v>
+        <v>70.8835</v>
       </c>
       <c r="F100">
-        <v>80.01700000000001</v>
+        <v>80.8335</v>
       </c>
       <c r="G100">
         <v>3.37</v>
@@ -9487,37 +9487,37 @@
         <v>8.22938775510204</v>
       </c>
       <c r="M100">
-        <v>16.0674136</v>
+        <v>16.2313668</v>
       </c>
       <c r="N100">
-        <v>-7.838025844897961</v>
+        <v>-8.00197904489796</v>
       </c>
       <c r="O100">
-        <v>-1.175703876734694</v>
+        <v>-1.200296856734694</v>
       </c>
       <c r="P100">
-        <v>-6.662321968163267</v>
+        <v>-6.801682188163266</v>
       </c>
       <c r="Q100">
-        <v>-1.422321968163267</v>
+        <v>-1.561682188163266</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.729702779750548</v>
+        <v>13.4136055595011</v>
       </c>
       <c r="T100">
-        <v>40.87791735717907</v>
+        <v>81.75583471435816</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07682681195592711</v>
+        <v>0.0760507835523319</v>
       </c>
       <c r="W100">
-        <v>0.1853731761592498</v>
+        <v>0.1855290026626918</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5121787463728474</v>
+        <v>0.5070052236822127</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.317809768231076</v>
-      </c>
-      <c r="C101">
-        <v>-34.02541890369985</v>
-      </c>
-      <c r="D101">
-        <v>43.43808109630015</v>
-      </c>
-      <c r="E101">
-        <v>70.8835</v>
-      </c>
-      <c r="F101">
-        <v>80.8335</v>
-      </c>
-      <c r="G101">
-        <v>3.37</v>
-      </c>
-      <c r="H101">
-        <v>71.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>13.46938775510204</v>
-      </c>
-      <c r="K101">
-        <v>5.24</v>
-      </c>
-      <c r="L101">
-        <v>8.22938775510204</v>
-      </c>
-      <c r="M101">
-        <v>16.2313668</v>
-      </c>
-      <c r="N101">
-        <v>-8.00197904489796</v>
-      </c>
-      <c r="O101">
-        <v>-1.200296856734694</v>
-      </c>
-      <c r="P101">
-        <v>-6.801682188163266</v>
-      </c>
-      <c r="Q101">
-        <v>-1.561682188163266</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>13.4136055595011</v>
-      </c>
-      <c r="T101">
-        <v>81.75583471435816</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.0760507835523319</v>
-      </c>
-      <c r="W101">
-        <v>0.1855290026626918</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5070052236822127</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
